--- a/Result/checksun_type/不鏽鋼胚.xlsx
+++ b/Result/checksun_type/不鏽鋼胚.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>31.65</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>32.62</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>34.35</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>34.35</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>88619.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>56397.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>56397</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>81909.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>71062.74</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>71062.74000000001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-6411.908493448966</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>88619</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>88619.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>31.41</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>32.66</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>34.41</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>34.41</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>30296.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>55604.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>55604.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>81238.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>75154.3</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>75154.3</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-9133.301158309303</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>30296</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>30296.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>31.37</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>32.78</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>34.54</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>34.54</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>51673.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>67354.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>67354.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>87056.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>76625.64</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>76625.64</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-6445.922781027301</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>51673</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>51673.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>31.34</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>32.94</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>34.65</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>32.94</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>34.65</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>47092.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>74374.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>74374.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>92061.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>76543.48</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>76543.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-4666.992142730625</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>47092</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>47092.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>31.32</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>33.13</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>34.77</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>33.13</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>34.77</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>64305.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>91626.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>91626</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>98215.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>76798.64</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>76798.64</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1468.16294006641</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>64305</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>64305.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>31.49</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>33.35</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>34.89</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>34.89</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>84657.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>107421.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>107421.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>104305.1</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>77733.42</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>77733.42</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>1309.777454456271</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>84657</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>84657.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>31.89</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>33.58</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>35.03</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>33.58</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>35.03</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>89047.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>106873.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>106873</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>107795.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>80213.18</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>80213.17999999999</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>3050.914537543809</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>89047</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>89047.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>32.3</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>33.83</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>35.15</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>35.15</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>86773.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>106758.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>106758.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>107839.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>79632.8</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>79632.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>4958.934851327998</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>86773</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>86773.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>32.75</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>34.07</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>35.27</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>35.27</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>133348.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>109748.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>109748</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>110112.7</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>80021.1</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>80021.10000000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>7751.216197757982</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>133348</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>133348.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>33.23</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>35.38</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>35.38</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>143284.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>104805.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>104805.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>105668.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>79834.04</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>79834.03999999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>6473.181828452303</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>143284</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>143284.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>33.52</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>34.47</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>35.5</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>35.5</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>81913.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>101188.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>101188.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>97048.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>81169.24</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>81169.24000000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>3351.661949856643</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>81913</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>81913.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>28.09</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>28.28</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>28.52</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>28.28</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>28.52</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>111.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>0</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>0.2114926513422688</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>111</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>28.17</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>28.29</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>28.54</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>28.54</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>0</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>0</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>28.84098236454781</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>0</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>28.11</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>28.33</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>28.55</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>28.55</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>423.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>387.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>387.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>402.7</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>0</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>28.84098236454781</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>423</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>423.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>28.2</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>28.35</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>28.56</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>28.56</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>277.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>325.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>325.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>398.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>0</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>26.47780232639076</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>277</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>277.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>28.25</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>28.34</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>28.56</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>28.56</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>506.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX17" t="n">
+        <v>374</v>
+      </c>
+      <c r="AY17" t="inlineStr">
         <is>
           <t>374.0</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>374.0</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>0</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>37.79905218879537</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>506</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>506.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>28.44</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>28.44</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>28.58</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>28.58</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>221.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>368.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>368</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>331.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>0</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>28.08658584263071</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>221</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>221.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>28.44</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>28.47</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>28.59</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>28.59</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>511.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>475.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>475.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>312.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>0</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>43.74425585373007</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>511</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>511.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>28.44</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>28.49</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>28.61</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>28.61</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>114.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>417.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>417.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>287.0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>0</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>33.47863244623875</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>114</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>28.4</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>28.61</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>28.61</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>518.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>471.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>471.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>281.4</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>0</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>60.15350499102834</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>518</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>518.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>28.35</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>28.62</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>28.62</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>476.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>374.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>374</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>0</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>52.82641201961962</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>476</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>476.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>28.29</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>28.54</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>28.62</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>28.54</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>28.62</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>757.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>295.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>295.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>0</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>44.97247877404934</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>757</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>757.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>28.99</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>30.08</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>28.2</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>28.2</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>1203482068.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>1387618376.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>1387618376.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>4264040487.3</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>3111629550.18</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>3111629550.18</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-488176249.5318046</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>1203482068</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>1203482068.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>29.02</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>30.16</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>28.07</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>30.16</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>28.07</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>942023312.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>1584381817.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>1584381817</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>4484329546.0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>3097694126.7</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>3097694126.7</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-425650424.2230182</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>942023312</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>942023312.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>29.25</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>30.24</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>27.94</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>27.94</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>1007778782.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>2139497377.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>2139497377.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>4665494634.0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>3096337448.26</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>3096337448.26</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-293112577.631073</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>1007778782</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1007778782.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>29.73</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>30.32</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>27.81</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>27.81</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>1607084998.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>3258049059.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>3258049059.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>4688553902.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>3083594155.06</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>3083594155.06</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-100349719.3700418</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>1607084998</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>1607084998.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>30.62</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>30.38</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>27.69</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>27.69</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>2177722724.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>5262265961.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>5262265961.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>4687463430.7</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>3075231109.06</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>3075231109.06</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>114398330.6946478</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>2177722724</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>31.58</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>30.41</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>27.56</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>30.41</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>27.56</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>2187299269.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>7140462597.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>7140462597.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>4678699401.4</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>3064464439.28</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>3064464439.28</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>355955848.3336811</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>2187299269</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>2187299269.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>32.04</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>30.44</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>27.46</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>27.46</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>3717601115.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>7384277275.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>7384277275</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>4600886187.9</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>3041422265.56</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>3041422265.56</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>687299249.1275253</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>3717601115</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>3717601115.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>32.03</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>30.45</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>27.29</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>27.29</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>6600537191.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>7191491890.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>7191491890.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>4454153458.5</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>2973288757.28</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>2973288757.28</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>972139650.7213211</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>6600537191</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>6600537191.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>31.7</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>30.34</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>27.1</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>27.1</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>11628169508.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>6119058745.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>6119058745.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>3965899981.1</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>2847760321.4</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>2847760321.4</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>1035449228.758123</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>11628169508</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>11628169508.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>31.07</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>30.19</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>26.9</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>26.9</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>11568705906.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>4112660900.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>4112660900</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>2972243250.2</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>2623033685.92</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>2623033685.92</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>550236262.3907671</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>11568705906</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>11568705906.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>30.27</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>29.82</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>26.66</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>26.66</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>3406372655.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>2216936205.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>2216936205</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>2119863690.1</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>2406749639.6</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>2406749639.6</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-156205313.0051274</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>3406372655</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>3406372655.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/不鏽鋼胚.xlsx
+++ b/Result/checksun_type/不鏽鋼胚.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1961.0</t>
+          <t>4838.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>8.10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>23.83</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1163,47 +1163,47 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.51</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>31.41</v>
+        <v>31.44</v>
       </c>
       <c r="BA2" t="n">
-        <v>32.59</v>
+        <v>32.52</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>33.91</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>57.53</t>
+          <t>71.83</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.16</v>
+        <v>-0.09</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.38</v>
+        <v>-0.33</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-112.21</t>
+          <t>-110.35</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>558187.1620305981</t>
+          <t>557740.3708333333</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>63315.0</t>
+          <t>157665.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>69320.60000000001</v>
+        <v>82604.8</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>65444.2</t>
+          <t>76417.1</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>73402.25999999999</v>
+        <v>75403.94</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-240.2277273371592</t>
+          <t>1103.212103168985</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>1787.620876668276</t>
+          <t>8492.13117095278</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>63315.0</t>
+          <t>157665.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2278.0</t>
+          <t>1961.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-34.60</t>
+          <t>-33.78</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1650,14 +1650,14 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.35</v>
+        <v>1.47</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1667,30 +1667,30 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>31.39</v>
+        <v>31.41</v>
       </c>
       <c r="BA3" t="n">
-        <v>32.66</v>
+        <v>32.59</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>33.91</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>57.53</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.25</v>
+        <v>-0.16</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.44</v>
+        <v>-0.38</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-113.96</t>
+          <t>-112.21</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>558187.1620305981</t>
+          <t>557740.3708333333</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>73004.0</t>
+          <t>63315.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>78126.60000000001</v>
+        <v>69320.60000000001</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>62199.4</t>
+          <t>65444.2</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>73508.56</v>
+        <v>73402.25999999999</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-608.9274735199656</t>
+          <t>-240.2277273371592</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>2254.833996380839</t>
+          <t>1787.620876668276</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>73004.0</t>
+          <t>63315.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-14.57</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
+          <t>32.2</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>32.45</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
           <t>31.9</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>32.25</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>31.75</t>
-        </is>
-      </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1732.0</t>
+          <t>2278.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>25.61</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-34.60</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,12 +2118,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2137,47 +2137,47 @@
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.3</v>
+        <v>0.35</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>31.42</v>
+        <v>31.39</v>
       </c>
       <c r="BA4" t="n">
-        <v>32.73</v>
+        <v>32.66</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>42.66</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.32</v>
+        <v>-0.25</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.49</v>
+        <v>-0.44</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-115.45</t>
+          <t>-113.96</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>558187.1620305981</t>
+          <t>557740.3708333333</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>55201.0</t>
+          <t>73004.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>71433.60000000001</v>
+        <v>78126.60000000001</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>58463.8</t>
+          <t>62199.4</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>73758</v>
+        <v>73508.56</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>12969</t>
+          <t>15927</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-1129.611377138294</t>
+          <t>-608.9274735199656</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>1803.644381813749</t>
+          <t>2254.833996380839</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>55201.0</t>
+          <t>73004.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-14.97</t>
+          <t>-14.57</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
+          <t>31.9</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>32.25</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>31.75</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
           <t>31.95</t>
-        </is>
-      </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>32.2</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>31.7</t>
-        </is>
-      </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>31.8</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2012.0</t>
+          <t>1732.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2439,12 +2439,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,12 +2605,12 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2620,51 +2620,51 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>2.02</v>
+        <v>1.53</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.72</v>
+        <v>-0.3</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>31.4</v>
+        <v>31.42</v>
       </c>
       <c r="BA5" t="n">
-        <v>32.79</v>
+        <v>32.73</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>34.07</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>26.22</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.39</v>
+        <v>-0.32</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.53</v>
+        <v>-0.49</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-116.77</t>
+          <t>-115.45</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>558187.1620305981</t>
+          <t>557740.3708333333</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>63839.0</t>
+          <t>55201.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>72984.60000000001</v>
+        <v>71433.60000000001</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>59601.5</t>
+          <t>58463.8</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>74001.36</v>
+        <v>73758</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>13383</t>
+          <t>12969</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-1662.930606038665</t>
+          <t>-1129.611377138294</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>3002.136204510287</t>
+          <t>1803.644381813749</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>63839.0</t>
+          <t>55201.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2849,17 +2849,17 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2939.0</t>
+          <t>2012.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-35.62</t>
+          <t>-34.90</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3107,51 +3107,51 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>1.13</v>
+        <v>2.02</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.88</v>
+        <v>-0.72</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>31.38</v>
+        <v>31.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>32.86</v>
+        <v>32.79</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>34.14</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>26.22</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.47</v>
+        <v>-0.39</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.53</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-117.87</t>
+          <t>-116.77</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>558187.1620305981</t>
+          <t>557740.3708333333</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>91244.0</t>
+          <t>63839.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>70229.39999999999</v>
+        <v>72984.60000000001</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>60410.7</t>
+          <t>59601.5</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>73497.5</v>
+        <v>74001.36</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-2511.12457159302</t>
+          <t>-1662.930606038665</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>3681.548229629974</t>
+          <t>3002.136204510287</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>91244.0</t>
+          <t>63839.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-15.91</t>
+          <t>-14.97</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3516.0</t>
+          <t>2939.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-37.56</t>
+          <t>-35.62</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-1.9</v>
+        <v>1.13</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.92</v>
+        <v>-0.88</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
         <v>31.38</v>
       </c>
       <c r="BA7" t="n">
-        <v>32.95</v>
+        <v>32.86</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>34.21</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.53</v>
+        <v>-0.47</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.59</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-118.59</t>
+          <t>-117.87</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>558187.1620305981</t>
+          <t>557740.3708333333</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>107345.0</t>
+          <t>91244.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>61567.8</v>
+        <v>70229.39999999999</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>55313.6</t>
+          <t>60410.7</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>72236</v>
+        <v>73497.5</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-3637.065080906292</t>
+          <t>-2511.12457159302</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>1584.402971599877</t>
+          <t>3681.548229629974</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>107345.0</t>
+          <t>91244.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-18.45</t>
+          <t>-15.91</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,17 +3758,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1275.0</t>
+          <t>3516.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-36.44</t>
+          <t>-37.56</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.58</v>
+        <v>-1.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.63</v>
+        <v>-0.92</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>31.09</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>31.43</v>
+        <v>31.38</v>
       </c>
       <c r="BA8" t="n">
-        <v>33.05</v>
+        <v>32.95</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>34.36</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>15.37</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.51</v>
+        <v>-0.53</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.6</v>
+        <v>-0.59</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-119.01</t>
+          <t>-118.59</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>558187.1620305981</t>
+          <t>557740.3708333333</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>39539.0</t>
+          <t>107345.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>46272.2</v>
+        <v>61567.8</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>49181.6</t>
+          <t>55313.6</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>71236.53999999999</v>
+        <v>72236</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-2909</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-4586.422908634687</t>
+          <t>-3637.065080906292</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-3193.211788857385</t>
+          <t>1584.402971599877</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>39539.0</t>
+          <t>107345.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-16.98</t>
+          <t>-18.45</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,17 +4245,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2033.0</t>
+          <t>1275.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,12 +4553,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4568,51 +4568,51 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>66.23</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.54</v>
+        <v>-0.58</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.63</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>31.23</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>31.44</v>
+        <v>31.43</v>
       </c>
       <c r="BA9" t="n">
-        <v>33.13</v>
+        <v>33.05</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>34.44</t>
+          <t>34.36</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>15.37</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.52</v>
+        <v>-0.51</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.62</v>
+        <v>-0.6</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-119.74</t>
+          <t>-119.01</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>558187.1620305981</t>
+          <t>557740.3708333333</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>62956.0</t>
+          <t>39539.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>45494</v>
+        <v>46272.2</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>49424.9</t>
+          <t>49181.6</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>71245.72</v>
+        <v>71236.53999999999</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-3930</t>
+          <t>-2909</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-4839.734021321469</t>
+          <t>-4586.422908634687</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-2639.40388276572</t>
+          <t>-3193.211788857385</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>62956.0</t>
+          <t>39539.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4797,17 +4797,17 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1583.0</t>
+          <t>2033.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-35.62</t>
+          <t>-36.44</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>66.23</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>0.83</v>
+        <v>-0.54</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.82</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>31.19</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>31.45</v>
+        <v>31.44</v>
       </c>
       <c r="BA10" t="n">
-        <v>33.22</v>
+        <v>33.13</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>34.51</t>
+          <t>34.44</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.54</v>
+        <v>-0.52</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.65</v>
+        <v>-0.62</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-120.53</t>
+          <t>-119.74</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>558187.1620305981</t>
+          <t>557740.3708333333</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>50063.0</t>
+          <t>62956.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>46218.4</v>
+        <v>45494</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>47730.5</t>
+          <t>49424.9</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>70713.39999999999</v>
+        <v>71245.72</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-1512</t>
+          <t>-3930</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-5239.794046513423</t>
+          <t>-4839.734021321469</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-4262.949592535988</t>
+          <t>-2639.40388276572</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>50063.0</t>
+          <t>62956.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-15.91</t>
+          <t>-16.98</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5289,17 +5289,17 @@
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1522.0</t>
+          <t>1583.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-35.72</t>
+          <t>-35.62</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>38.62</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.98</v>
+        <v>-0.82</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>31.13</t>
+          <t>31.19</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>31.44</v>
+        <v>31.45</v>
       </c>
       <c r="BA11" t="n">
-        <v>33.3</v>
+        <v>33.22</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>34.59</t>
+          <t>34.51</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>13.53</t>
+          <t>17.31</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.58</v>
+        <v>-0.54</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.68</v>
+        <v>-0.65</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-121.42</t>
+          <t>-120.53</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>558187.1620305981</t>
+          <t>557740.3708333333</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>47936.0</t>
+          <t>50063.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>50592</v>
+        <v>46218.4</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>45632.9</t>
+          <t>47730.5</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>70428.03999999999</v>
+        <v>70713.39999999999</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>-1512</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-5417.402129054775</t>
+          <t>-5239.794046513423</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-5048.65954961723</t>
+          <t>-4262.949592535988</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>47936.0</t>
+          <t>50063.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-16.04</t>
+          <t>-15.91</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-19.97</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -6057,7 +6057,7 @@
         <v>28.16</v>
       </c>
       <c r="BA12" t="n">
-        <v>28.32</v>
+        <v>28.31</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
@@ -6066,14 +6066,14 @@
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>57.81</t>
+          <t>72.12</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-118.06</t>
+          <t>-115.30</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6101,34 +6101,34 @@
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>318.2</v>
+        <v>264.2</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>317.125</t>
+          <t>330.125</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>252.51</v>
+        <v>252.14</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-65</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>11.54386323394459</t>
+          <t>10.57768604337278</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>10.20830544829005</t>
+          <t>5.263711495227881</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6295,7 +6295,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -6520,14 +6520,14 @@
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.21</v>
+        <v>0.5</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -6537,30 +6537,30 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
         <v>28.16</v>
       </c>
       <c r="BA13" t="n">
-        <v>28.33</v>
+        <v>28.32</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>57.81</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-118.06</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6588,34 +6588,34 @@
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>263</v>
+        <v>318.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>340.225</t>
+          <t>317.125</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>254.55</v>
+        <v>252.51</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>11.78669192224541</t>
+          <t>11.54386323394459</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>7.264571615225691</t>
+          <t>10.20830544829005</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>263.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -7007,31 +7007,31 @@
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>1.14</v>
+        <v>0.71</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.52</v>
+        <v>-0.21</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>28.12</v>
+        <v>28.16</v>
       </c>
       <c r="BA14" t="n">
-        <v>28.36</v>
+        <v>28.33</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
@@ -7040,14 +7040,14 @@
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-122.89</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7071,38 +7071,38 @@
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>328.6</v>
+        <v>263</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>322.425</t>
+          <t>340.225</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>249.89</v>
+        <v>254.55</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-77</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>12.60889561443081</t>
+          <t>11.78669192224541</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>10.19264572458985</t>
+          <t>7.264571615225691</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>263.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7167,12 +7167,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
@@ -7232,17 +7232,17 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7490,48 +7490,48 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.8</v>
+        <v>-0.52</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="AZ15" t="n">
         <v>28.12</v>
       </c>
       <c r="BA15" t="n">
-        <v>28.37</v>
+        <v>28.36</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BE15" t="n">
         <v>-0.1</v>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-122.89</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7558,38 +7558,38 @@
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>386.25</v>
+        <v>328.6</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>336.525</t>
+          <t>322.425</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>259.19</v>
+        <v>249.89</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>13.04821377622008</t>
+          <t>12.60889561443081</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>39.19015710494619</t>
+          <t>10.19264572458985</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
@@ -7756,7 +7756,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>33.52</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7977,28 +7977,28 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AV16" t="n">
-        <v>-1.08</v>
+        <v>-0.8</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="AZ16" t="n">
@@ -8009,16 +8009,16 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-25.75</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="BE16" t="n">
         <v>-0.1</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-124.65</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8045,38 +8045,38 @@
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>512.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>396.05</v>
+        <v>386.25</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>296.625</t>
+          <t>336.525</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>251.79</v>
+        <v>259.19</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>49</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>8.29513317099715</t>
+          <t>13.04821377622008</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>33.35838203742151</t>
+          <t>39.19015710494619</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>512.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
@@ -8206,17 +8206,17 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
+          <t>28.35</t>
+        </is>
+      </c>
+      <c r="CS16" t="inlineStr">
+        <is>
           <t>28.3</t>
-        </is>
-      </c>
-      <c r="CS16" t="inlineStr">
-        <is>
-          <t>28.0</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>25.90</t>
+          <t>33.52</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-15.74</t>
+          <t>-12.65</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8459,28 +8459,28 @@
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AV17" t="n">
-        <v>-1.11</v>
+        <v>-1.08</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -8489,10 +8489,10 @@
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>28.13</v>
+        <v>28.12</v>
       </c>
       <c r="BA17" t="n">
-        <v>28.38</v>
+        <v>28.37</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
@@ -8501,11 +8501,11 @@
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-75.27</t>
+          <t>-25.75</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.17</v>
+        <v>-0.13</v>
       </c>
       <c r="BE17" t="n">
         <v>-0.1</v>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-123.06</t>
+          <t>-124.65</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8532,38 +8532,38 @@
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>512.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>316.05</v>
+        <v>396.05</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>251.025</t>
+          <t>296.625</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>242.12</v>
+        <v>251.79</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>99</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>3.738178831647267</t>
+          <t>8.29513317099715</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>17.83590401104965</t>
+          <t>33.35838203742151</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>512.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,17 +8628,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>68.17</t>
+          <t>25.90</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.51</t>
+          <t>-15.74</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8955,47 +8955,47 @@
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-1.14</v>
+        <v>-1.87</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.49</v>
+        <v>-1.11</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>28.16</v>
+        <v>28.13</v>
       </c>
       <c r="BA18" t="n">
-        <v>28.4</v>
+        <v>28.38</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-46.29</t>
+          <t>-75.27</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.11</v>
+        <v>-0.17</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-118.72</t>
+          <t>-123.06</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9019,38 +9019,38 @@
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>591.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>417.45</v>
+        <v>316.05</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>248.225</t>
+          <t>251.025</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>241.58</v>
+        <v>242.12</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>1.174956071755924</t>
+          <t>3.738178831647267</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>43.88108168726677</t>
+          <t>17.83590401104965</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>591.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,149 +9242,149 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>27.7</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>68.17</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2024-11-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2024-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>32.65</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>32.4</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>32.95</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-14.51</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
           <t>27.9</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>60.51</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2024-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2024-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>32.4</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>-13.89</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
       <c r="AI19" t="inlineStr">
         <is>
           <t>2025/11/26</t>
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9438,14 +9438,14 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-0.85</v>
+        <v>-1.14</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.12</v>
+        <v>-0.49</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
@@ -9454,36 +9454,36 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>28.17</v>
+        <v>28.16</v>
       </c>
       <c r="BA19" t="n">
-        <v>28.41</v>
+        <v>28.4</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-21.70</t>
+          <t>-46.29</t>
         </is>
       </c>
       <c r="BD19" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="BE19" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BE19" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
       <c r="BF19" t="inlineStr">
         <is>
           <t>0.42</t>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-116.56</t>
+          <t>-118.72</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9506,38 +9506,38 @@
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>591.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>316.25</v>
+        <v>417.45</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>197.025</t>
+          <t>248.225</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>230.32</v>
+        <v>241.58</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>169</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-6.589794040155141</t>
+          <t>1.174956071755924</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>22.19986830731742</t>
+          <t>43.88108168726677</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>316.25</t>
+          <t>591.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9704,7 +9704,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>60.51</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9925,18 +9925,18 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-1.13</v>
+        <v>-0.85</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.15</v>
+        <v>-0.12</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -9946,27 +9946,27 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>28.22</t>
+          <t>28.14</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>28.18</v>
+        <v>28.17</v>
       </c>
       <c r="BA20" t="n">
-        <v>28.42</v>
+        <v>28.41</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>28.52</t>
+          <t>28.51</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-21.70</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="BE20" t="n">
         <v>-0.07000000000000001</v>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-115.66</t>
+          <t>-116.56</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9993,38 +9993,38 @@
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>505.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>286.8</v>
+        <v>316.25</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>176.7</t>
+          <t>197.025</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>224.76</v>
+        <v>230.32</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>119</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-11.82427810333197</t>
+          <t>-6.589794040155141</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>19.87135389641412</t>
+          <t>22.19986830731742</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>505.0</t>
+          <t>316.25</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
@@ -10154,17 +10154,17 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,139 +10216,139 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>27.9</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>62.31</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2024-11-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2024-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>32.65</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>32.4</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>32.95</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-13.89</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
           <t>28.3</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>37.90</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2024-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2024-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>32.4</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>-12.65</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
       <c r="AG21" t="inlineStr">
         <is>
           <t>2025/12/16</t>
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10407,53 +10407,53 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>0.14</v>
+        <v>-1.13</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>28.26</t>
+          <t>28.22</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>28.22</v>
+        <v>28.18</v>
       </c>
       <c r="BA21" t="n">
-        <v>28.44</v>
+        <v>28.42</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>28.52</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>40.40</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="BE21" t="n">
         <v>-0.07000000000000001</v>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-115.70</t>
+          <t>-115.66</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10480,38 +10480,38 @@
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>505.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>197.2</v>
+        <v>286.8</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>176.7</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>215.04</v>
+        <v>224.76</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>110</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-17.58712028510399</t>
+          <t>-11.82427810333197</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-4.388000758319691</t>
+          <t>19.87135389641412</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>505.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>201756.824</t>
+          <t>201436.815</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10718,12 +10718,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>45.52</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>56.96</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-7.43</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,600</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>201757</t>
+          <t>201437</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.25</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>79.17</t>
+          <t>87.64</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>7.21</v>
+        <v>1.96</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.68</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>30.45</v>
+        <v>30.59</v>
       </c>
       <c r="BA22" t="n">
-        <v>30.21</v>
+        <v>30.26</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>87.50</t>
+          <t>76.40</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-87.65</t>
+          <t>-84.73</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,48 +10962,48 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>1706003222.352083</t>
+          <t>1717531030.886963</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>6703778205.0</t>
+          <t>6678368784.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>3070110512.8</v>
+        <v>4210288560.2</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>2633033521.2</t>
+          <t>2893256394.5</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>2766125687.26</v>
+        <v>2808126948.8</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>437076991</t>
+          <t>1317032165</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-39252013.91480508</t>
+          <t>67944137.9742843</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>446580799.0531235</t>
+          <t>657522973.3642759</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>6703778205.0</t>
+          <t>6678368784.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -11063,22 +11063,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>92.92</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>148228</t>
+          <t>143132</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="CW22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>173832.442</t>
+          <t>201756.824</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,177 +11190,177 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>33.45</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-3.56</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1.71</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>16.60</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-12-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-12-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>31.65</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>5.38</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-9.73</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>31.65</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>5.69</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
         <is>
           <t>2025-12-24 00:00:00</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-12-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>2025-12-24 00:00:00</t>
-        </is>
-      </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,67 +11371,67 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,600</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>201757</t>
+          <t>201437</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>59.72</t>
+          <t>79.17</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>4.08</v>
+        <v>7.21</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.45</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>7.40</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>30.24</v>
+        <v>30.45</v>
       </c>
       <c r="BA23" t="n">
-        <v>30.08</v>
+        <v>30.21</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>28.01</t>
+          <t>28.14</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>87.50</t>
         </is>
       </c>
       <c r="BD23" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BE23" t="n">
         <v>0.25</v>
       </c>
-      <c r="BE23" t="n">
-        <v>0.2</v>
-      </c>
       <c r="BF23" t="inlineStr">
         <is>
           <t>2.05</t>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-90.35</t>
+          <t>-87.65</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,48 +11449,48 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>1706003222.352083</t>
+          <t>1717531030.886963</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>5573788437.0</t>
+          <t>6703778205.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>1865132854</v>
+        <v>3070110512.8</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>2066069442.4</t>
+          <t>2633033521.2</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>2676628654.12</v>
+        <v>2766125687.26</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-200936588</t>
+          <t>437076991</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-127585252.6362467</t>
+          <t>-39252013.91480508</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>126563083.5352938</t>
+          <t>446580799.0531235</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>5573788437.0</t>
+          <t>6703778205.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>92.92</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>148228</t>
+          <t>143132</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>32.45</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11645,14 +11645,14 @@
       </c>
       <c r="CW23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>24919.15</t>
+          <t>173832.442</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,22 +11687,22 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-33.78</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,87 +11837,87 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,600</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>201757</t>
+          <t>201437</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>35.42</t>
+          <t>59.72</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>1.63</v>
+        <v>4.08</v>
       </c>
       <c r="AV24" t="n">
-        <v>-0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>7.40</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>30.1</v>
+        <v>30.24</v>
       </c>
       <c r="BA24" t="n">
-        <v>30.01</v>
+        <v>30.08</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-91.01</t>
+          <t>-90.35</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,48 +11936,48 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>1706003222.352083</t>
+          <t>1717531030.886963</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>759763435.0</t>
+          <t>5573788437.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>1077793893.4</v>
+        <v>1865132854</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>1627503444.5</t>
+          <t>2066069442.4</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>2702285145.58</v>
+        <v>2676628654.12</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>-549709551</t>
+          <t>-200936588</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>-173794041.0310722</t>
+          <t>-127585252.6362467</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-214054859.3307233</t>
+          <t>126563083.5352938</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>759763435.0</t>
+          <t>5573788437.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12037,22 +12037,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>92.92</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>148228</t>
+          <t>143132</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="CW24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>43906.141</t>
+          <t>24919.15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-17.87</t>
+          <t>-33.78</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,66 +12345,66 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,600</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>201757</t>
+          <t>201437</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="AV25" t="n">
-        <v>-0.65</v>
+        <v>-0.14</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>30.04</v>
+        <v>30.1</v>
       </c>
       <c r="BA25" t="n">
-        <v>30.02</v>
+        <v>30.01</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-36.09</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-90.57</t>
+          <t>-91.01</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>1706003222.352083</t>
+          <t>1717531030.886963</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>1335743940.0</t>
+          <t>759763435.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>1395419891.4</v>
+        <v>1077793893.4</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>1699043008.9</t>
+          <t>1627503444.5</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>2792941015.34</v>
+        <v>2702285145.58</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>-303623117</t>
+          <t>-549709551</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-166473892.2493175</t>
+          <t>-173794041.0310722</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-177218711.0917931</t>
+          <t>-214054859.3307233</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>1335743940.0</t>
+          <t>759763435.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>92.92</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>148228</t>
+          <t>143132</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12619,14 +12619,14 @@
       </c>
       <c r="CW25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>32757.289</t>
+          <t>43906.141</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-17.87</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,66 +12832,66 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,600</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>201757</t>
+          <t>201437</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>-0.1</v>
+        <v>2.04</v>
       </c>
       <c r="AV26" t="n">
-        <v>-0.08</v>
+        <v>-0.65</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>8.41</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>29.93</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>29.96</v>
+        <v>30.04</v>
       </c>
       <c r="BA26" t="n">
-        <v>30.05</v>
+        <v>30.02</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>27.72</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-51.90</t>
+          <t>-36.09</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-89.71</t>
+          <t>-90.57</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>1706003222.352083</t>
+          <t>1717531030.886963</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>977478547.0</t>
+          <t>1335743940.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>1576224228.8</v>
+        <v>1395419891.4</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>1778829403.7</t>
+          <t>1699043008.9</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>2993188486.96</v>
+        <v>2792941015.34</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-202605174</t>
+          <t>-303623117</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>-164520288.8234128</t>
+          <t>-166473892.2493175</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-179978599.4614716</t>
+          <t>-177218711.0917931</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>977478547.0</t>
+          <t>1335743940.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13011,22 +13011,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>92.92</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>148228</t>
+          <t>143132</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="CW26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22912.409</t>
+          <t>32757.289</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,177 +13138,177 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>29.9</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>7.43</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-1.71</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-11.39</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2025-12-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2025-12-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>31.65</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>11.81</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>22.49</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="AK27" t="inlineStr">
         <is>
           <t>2025-12-24 00:00:00</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2025-12-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>2025-12-24 00:00:00</t>
-        </is>
-      </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,600</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>201757</t>
+          <t>201437</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>-2.7</v>
+        <v>-0.1</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.48</v>
+        <v>-0.08</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>8.41</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>29.93</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>29.88</v>
+        <v>29.96</v>
       </c>
       <c r="BA27" t="n">
         <v>30.05</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>27.64</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-46.45</t>
+          <t>-51.90</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-88.38</t>
+          <t>-89.71</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>1706003222.352083</t>
+          <t>1717531030.886963</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>678889911.0</t>
+          <t>977478547.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>2195956529.6</v>
+        <v>1576224228.8</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>1792692633.0</t>
+          <t>1778829403.7</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>3146696765.1</v>
+        <v>2993188486.96</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>403263896</t>
+          <t>-202605174</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-161709686.8892204</t>
+          <t>-164520288.8234128</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-139107912.1873884</t>
+          <t>-179978599.4614716</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>678889911.0</t>
+          <t>977478547.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13498,22 +13498,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>92.92</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>148228</t>
+          <t>143132</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
+          <t>29.8</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>30.1</t>
+        </is>
+      </c>
+      <c r="CS27" t="inlineStr">
+        <is>
           <t>29.6</t>
         </is>
       </c>
-      <c r="CR27" t="inlineStr">
-        <is>
-          <t>29.95</t>
-        </is>
-      </c>
-      <c r="CS27" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="CW27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>54441.068</t>
+          <t>22912.409</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,38 +13806,38 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,600</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>201757</t>
+          <t>201437</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>-1.39</v>
+        <v>-2.7</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -13849,23 +13849,23 @@
         <v>29.88</v>
       </c>
       <c r="BA28" t="n">
-        <v>30.02</v>
+        <v>30.05</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>27.64</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-24.87</t>
+          <t>-46.45</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="BE28" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-87.03</t>
+          <t>-88.38</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>1706003222.352083</t>
+          <t>1717531030.886963</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>1637093634.0</t>
+          <t>678889911.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>2267006030.8</v>
+        <v>2195956529.6</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>1933953822.0</t>
+          <t>1792692633.0</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>3226284926.5</v>
+        <v>3146696765.1</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>333052208</t>
+          <t>403263896</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-165819100.4713716</t>
+          <t>-161709686.8892204</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-43761436.78914857</t>
+          <t>-139107912.1873884</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>1637093634.0</t>
+          <t>678889911.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -13985,22 +13985,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>92.92</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>148228</t>
+          <t>143132</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="CW28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -14097,12 +14097,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>78847.301</t>
+          <t>54441.068</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -14112,177 +14112,177 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>29.9</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>7.43</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-1.71</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>17.22</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2025-12-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2025-12-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>31.65</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
           <t>29.45</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>11.96</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>13.67</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
         <is>
           <t>2025-12-24 00:00:00</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2025-12-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>-7.54</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>2025-12-24 00:00:00</t>
-        </is>
-      </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -14293,38 +14293,38 @@
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,600</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>201757</t>
+          <t>201437</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>53.19</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="AU29" t="n">
-        <v>-2.87</v>
+        <v>-1.39</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -14333,26 +14333,26 @@
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>29.84</v>
+        <v>29.88</v>
       </c>
       <c r="BA29" t="n">
-        <v>29.92</v>
+        <v>30.02</v>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-12.08</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="BD29" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>-86.22</t>
+          <t>-87.03</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
@@ -14371,48 +14371,48 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>1706003222.352083</t>
+          <t>1717531030.886963</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
         <is>
-          <t>2347893425.0</t>
+          <t>1637093634.0</t>
         </is>
       </c>
       <c r="BK29" t="n">
-        <v>2177212995.6</v>
+        <v>2267006030.8</v>
       </c>
       <c r="BL29" t="inlineStr">
         <is>
-          <t>1915411140.1</t>
+          <t>1933953822.0</t>
         </is>
       </c>
       <c r="BM29" t="n">
-        <v>3205376660.36</v>
+        <v>3226284926.5</v>
       </c>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>261801855</t>
+          <t>333052208</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>-188011402.9590485</t>
+          <t>-165819100.4713716</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>-8653962.37062192</t>
+          <t>-43761436.78914857</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>2347893425.0</t>
+          <t>1637093634.0</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="BU29" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="BV29" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -14472,22 +14472,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="CI29" t="inlineStr">
         <is>
-          <t>92.92</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="CJ29" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
         <is>
-          <t>148228</t>
+          <t>143132</t>
         </is>
       </c>
       <c r="CN29" t="inlineStr">
@@ -14537,22 +14537,22 @@
       </c>
       <c r="CQ29" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CR29" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CT29" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CU29" t="inlineStr">
@@ -14567,14 +14567,14 @@
       </c>
       <c r="CW29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -14584,12 +14584,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>71652.364</t>
+          <t>78847.301</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -14609,17 +14609,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -14759,17 +14759,17 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -14780,66 +14780,66 @@
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,600</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>201757</t>
+          <t>201437</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>59.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>53.19</t>
         </is>
       </c>
       <c r="AU30" t="n">
-        <v>1.08</v>
+        <v>-2.87</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>29.89</v>
+        <v>29.84</v>
       </c>
       <c r="BA30" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>21.13</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="BD30" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="BE30" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-86.22</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -14858,43 +14858,43 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>1706003222.352083</t>
+          <t>1717531030.886963</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
-          <t>2239765627.0</t>
+          <t>2347893425.0</t>
         </is>
       </c>
       <c r="BK30" t="n">
-        <v>2002666126.4</v>
+        <v>2177212995.6</v>
       </c>
       <c r="BL30" t="inlineStr">
         <is>
-          <t>1855304078.9</t>
+          <t>1915411140.1</t>
         </is>
       </c>
       <c r="BM30" t="n">
-        <v>3181037509.62</v>
+        <v>3205376660.36</v>
       </c>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>147362047</t>
+          <t>261801855</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>-220621846.7023988</t>
+          <t>-188011402.9590485</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>-34348477.86663342</t>
+          <t>-8653962.37062192</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>2239765627.0</t>
+          <t>2347893425.0</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="BU30" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="BV30" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="CI30" t="inlineStr">
         <is>
-          <t>92.92</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="CJ30" t="inlineStr">
@@ -14999,12 +14999,12 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
         <is>
-          <t>148228</t>
+          <t>143132</t>
         </is>
       </c>
       <c r="CN30" t="inlineStr">
@@ -15024,22 +15024,22 @@
       </c>
       <c r="CQ30" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CR30" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CT30" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CU30" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="CW30" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -15071,12 +15071,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>130253.713</t>
+          <t>71652.364</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -15086,177 +15086,177 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>30.9</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-1.71</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>7.94</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2025-12-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2025-12-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>31.65</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
           <t>31.85</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>4.78</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>11.55</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>-2.98</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
         <is>
           <t>2025-12-24 00:00:00</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2025-12-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>2025-12-24 00:00:00</t>
-        </is>
-      </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -15267,66 +15267,66 @@
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,600</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>201757</t>
+          <t>201437</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>59.57</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="AU31" t="n">
-        <v>4.02</v>
+        <v>1.08</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>29.9</v>
+        <v>29.89</v>
       </c>
       <c r="BA31" t="n">
-        <v>29.74</v>
+        <v>29.84</v>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>21.13</t>
         </is>
       </c>
       <c r="BD31" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="BE31" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>-86.56</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
@@ -15345,43 +15345,43 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>1706003222.352083</t>
+          <t>1717531030.886963</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
         <is>
-          <t>4076140051.0</t>
+          <t>2239765627.0</t>
         </is>
       </c>
       <c r="BK31" t="n">
-        <v>1981434578.6</v>
+        <v>2002666126.4</v>
       </c>
       <c r="BL31" t="inlineStr">
         <is>
-          <t>1776251770.7</t>
+          <t>1855304078.9</t>
         </is>
       </c>
       <c r="BM31" t="n">
-        <v>3174035525.9</v>
+        <v>3181037509.62</v>
       </c>
       <c r="BN31" t="inlineStr">
         <is>
-          <t>205182807</t>
+          <t>147362047</t>
         </is>
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>-254489731.9452652</t>
+          <t>-220621846.7023988</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>-58243076.00855589</t>
+          <t>-34348477.86663342</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>4076140051.0</t>
+          <t>2239765627.0</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="BU31" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BV31" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
@@ -15456,12 +15456,12 @@
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -15471,7 +15471,7 @@
       </c>
       <c r="CI31" t="inlineStr">
         <is>
-          <t>92.92</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="CJ31" t="inlineStr">
@@ -15486,12 +15486,12 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
         <is>
-          <t>148228</t>
+          <t>143132</t>
         </is>
       </c>
       <c r="CN31" t="inlineStr">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="CQ31" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CR31" t="inlineStr">
@@ -15521,12 +15521,12 @@
       </c>
       <c r="CS31" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CT31" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="CU31" t="inlineStr">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="CW31" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/不鏽鋼胚.xlsx
+++ b/Result/checksun_type/不鏽鋼胚.xlsx
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【d1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,42 +948,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.77</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1966.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>32.1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>4838.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>32.35</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-33.78</t>
+          <t>-34.29</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>23.83</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,66 +1144,66 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>31.44</v>
+        <v>31.45</v>
       </c>
       <c r="BA2" t="n">
-        <v>32.52</v>
+        <v>32.44</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>33.79</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>71.83</t>
+          <t>79.88</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.33</v>
+        <v>-0.27</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-110.35</t>
+          <t>-108.63</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>557740.3708333333</t>
+          <t>557097.1061026353</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>157665.0</t>
+          <t>62631.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>82604.8</v>
+        <v>82363.2</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>76417.1</t>
+          <t>77673.9</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>75403.94</v>
+        <v>75816.44</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>1103.212103168985</t>
+          <t>1832.784871555003</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>8492.13117095278</t>
+          <t>5845.435097678099</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>157665.0</t>
+          <t>62631.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-14.17</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1961.0</t>
+          <t>4838.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>8.10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>23.83</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1650,47 +1650,47 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>1.51</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>31.41</v>
+        <v>31.44</v>
       </c>
       <c r="BA3" t="n">
-        <v>32.59</v>
+        <v>32.52</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>33.91</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>57.53</t>
+          <t>71.83</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.16</v>
+        <v>-0.09</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.38</v>
+        <v>-0.33</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-112.21</t>
+          <t>-110.35</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>557740.3708333333</t>
+          <t>557097.1061026353</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>63315.0</t>
+          <t>157665.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>69320.60000000001</v>
+        <v>82604.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>65444.2</t>
+          <t>76417.1</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>73402.25999999999</v>
+        <v>75403.94</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-240.2277273371592</t>
+          <t>1103.212103168985</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>1787.620876668276</t>
+          <t>8492.13117095278</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>63315.0</t>
+          <t>157665.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2278.0</t>
+          <t>1961.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-34.60</t>
+          <t>-33.78</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,12 +2118,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2137,14 +2137,14 @@
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.35</v>
+        <v>1.47</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -2154,30 +2154,30 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>31.39</v>
+        <v>31.41</v>
       </c>
       <c r="BA4" t="n">
-        <v>32.66</v>
+        <v>32.59</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>33.91</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>57.53</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.25</v>
+        <v>-0.16</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.44</v>
+        <v>-0.38</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-113.96</t>
+          <t>-112.21</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>557740.3708333333</t>
+          <t>557097.1061026353</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>73004.0</t>
+          <t>63315.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>78126.60000000001</v>
+        <v>69320.60000000001</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>62199.4</t>
+          <t>65444.2</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>73508.56</v>
+        <v>73402.25999999999</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-608.9274735199656</t>
+          <t>-240.2277273371592</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>2254.833996380839</t>
+          <t>1787.620876668276</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>73004.0</t>
+          <t>63315.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-14.57</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
+          <t>32.2</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>32.45</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
           <t>31.9</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>32.25</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>31.75</t>
-        </is>
-      </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1732.0</t>
+          <t>2278.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>25.61</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-34.60</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,12 +2605,12 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2624,47 +2624,47 @@
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.3</v>
+        <v>0.35</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>31.42</v>
+        <v>31.39</v>
       </c>
       <c r="BA5" t="n">
-        <v>32.73</v>
+        <v>32.66</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>42.66</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.32</v>
+        <v>-0.25</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.49</v>
+        <v>-0.44</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-115.45</t>
+          <t>-113.96</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>557740.3708333333</t>
+          <t>557097.1061026353</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>55201.0</t>
+          <t>73004.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>71433.60000000001</v>
+        <v>78126.60000000001</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>58463.8</t>
+          <t>62199.4</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>73758</v>
+        <v>73508.56</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>12969</t>
+          <t>15927</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-1129.611377138294</t>
+          <t>-608.9274735199656</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>1803.644381813749</t>
+          <t>2254.833996380839</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>55201.0</t>
+          <t>73004.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-14.97</t>
+          <t>-14.57</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
+          <t>31.9</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>32.25</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>31.75</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
           <t>31.95</t>
-        </is>
-      </c>
-      <c r="CR5" t="inlineStr">
-        <is>
-          <t>32.2</t>
-        </is>
-      </c>
-      <c r="CS5" t="inlineStr">
-        <is>
-          <t>31.7</t>
-        </is>
-      </c>
-      <c r="CT5" t="inlineStr">
-        <is>
-          <t>31.8</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2012.0</t>
+          <t>1732.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3107,51 +3107,51 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>2.02</v>
+        <v>1.53</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.72</v>
+        <v>-0.3</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>31.4</v>
+        <v>31.42</v>
       </c>
       <c r="BA6" t="n">
-        <v>32.79</v>
+        <v>32.73</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>34.07</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>26.22</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.39</v>
+        <v>-0.32</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.53</v>
+        <v>-0.49</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-116.77</t>
+          <t>-115.45</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>557740.3708333333</t>
+          <t>557097.1061026353</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>63839.0</t>
+          <t>55201.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>72984.60000000001</v>
+        <v>71433.60000000001</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>59601.5</t>
+          <t>58463.8</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>74001.36</v>
+        <v>73758</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>13383</t>
+          <t>12969</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1662.930606038665</t>
+          <t>-1129.611377138294</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>3002.136204510287</t>
+          <t>1803.644381813749</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>63839.0</t>
+          <t>55201.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,17 +3336,17 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2939.0</t>
+          <t>2012.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-35.62</t>
+          <t>-34.90</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,12 +3579,12 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3594,51 +3594,51 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>1.13</v>
+        <v>2.02</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.88</v>
+        <v>-0.72</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>31.38</v>
+        <v>31.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>32.86</v>
+        <v>32.79</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>34.14</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>26.22</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.47</v>
+        <v>-0.39</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.53</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-117.87</t>
+          <t>-116.77</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>557740.3708333333</t>
+          <t>557097.1061026353</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>91244.0</t>
+          <t>63839.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>70229.39999999999</v>
+        <v>72984.60000000001</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>60410.7</t>
+          <t>59601.5</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>73497.5</v>
+        <v>74001.36</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-2511.12457159302</t>
+          <t>-1662.930606038665</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>3681.548229629974</t>
+          <t>3002.136204510287</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>91244.0</t>
+          <t>63839.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-15.91</t>
+          <t>-14.97</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3516.0</t>
+          <t>2939.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-37.56</t>
+          <t>-35.62</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-1.9</v>
+        <v>1.13</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.92</v>
+        <v>-0.88</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
         <v>31.38</v>
       </c>
       <c r="BA8" t="n">
-        <v>32.95</v>
+        <v>32.86</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>34.21</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.53</v>
+        <v>-0.47</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.59</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-118.59</t>
+          <t>-117.87</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>557740.3708333333</t>
+          <t>557097.1061026353</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>107345.0</t>
+          <t>91244.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>61567.8</v>
+        <v>70229.39999999999</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>55313.6</t>
+          <t>60410.7</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>72236</v>
+        <v>73497.5</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-3637.065080906292</t>
+          <t>-2511.12457159302</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>1584.402971599877</t>
+          <t>3681.548229629974</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>107345.0</t>
+          <t>91244.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-18.45</t>
+          <t>-15.91</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1275.0</t>
+          <t>3516.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-36.44</t>
+          <t>-37.56</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,66 +4553,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.58</v>
+        <v>-1.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.63</v>
+        <v>-0.92</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>31.09</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>31.43</v>
+        <v>31.38</v>
       </c>
       <c r="BA9" t="n">
-        <v>33.05</v>
+        <v>32.95</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>34.36</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>15.37</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.51</v>
+        <v>-0.53</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.6</v>
+        <v>-0.59</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-119.01</t>
+          <t>-118.59</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>557740.3708333333</t>
+          <t>557097.1061026353</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>39539.0</t>
+          <t>107345.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>46272.2</v>
+        <v>61567.8</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>49181.6</t>
+          <t>55313.6</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>71236.53999999999</v>
+        <v>72236</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-2909</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-4586.422908634687</t>
+          <t>-3637.065080906292</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-3193.211788857385</t>
+          <t>1584.402971599877</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>39539.0</t>
+          <t>107345.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-16.98</t>
+          <t>-18.45</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2033.0</t>
+          <t>1275.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,12 +5040,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5055,51 +5055,51 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>66.23</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.54</v>
+        <v>-0.58</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.63</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>31.23</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>31.44</v>
+        <v>31.43</v>
       </c>
       <c r="BA10" t="n">
-        <v>33.13</v>
+        <v>33.05</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>34.44</t>
+          <t>34.36</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>15.37</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.52</v>
+        <v>-0.51</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.62</v>
+        <v>-0.6</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-119.74</t>
+          <t>-119.01</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>557740.3708333333</t>
+          <t>557097.1061026353</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>62956.0</t>
+          <t>39539.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>45494</v>
+        <v>46272.2</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>49424.9</t>
+          <t>49181.6</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>71245.72</v>
+        <v>71236.53999999999</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-3930</t>
+          <t>-2909</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-4839.734021321469</t>
+          <t>-4586.422908634687</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-2639.40388276572</t>
+          <t>-3193.211788857385</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>62956.0</t>
+          <t>39539.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,17 +5284,17 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1583.0</t>
+          <t>2033.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-35.62</t>
+          <t>-36.44</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>66.23</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>0.83</v>
+        <v>-0.54</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.82</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>31.19</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>31.45</v>
+        <v>31.44</v>
       </c>
       <c r="BA11" t="n">
-        <v>33.22</v>
+        <v>33.13</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>34.51</t>
+          <t>34.44</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.54</v>
+        <v>-0.52</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.65</v>
+        <v>-0.62</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-120.53</t>
+          <t>-119.74</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>557740.3708333333</t>
+          <t>557097.1061026353</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>50063.0</t>
+          <t>62956.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>46218.4</v>
+        <v>45494</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>47730.5</t>
+          <t>49424.9</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>70713.39999999999</v>
+        <v>71245.72</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-1512</t>
+          <t>-3930</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-5239.794046513423</t>
+          <t>-4839.734021321469</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-4262.949592535988</t>
+          <t>-2639.40388276572</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>50063.0</t>
+          <t>62956.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-15.91</t>
+          <t>-16.98</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5776,17 +5776,17 @@
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-19.97</t>
+          <t>-36.76</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -6014,7 +6014,7 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -6036,16 +6036,16 @@
         <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
           <t>-0.53</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>-0.47</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -6057,90 +6057,90 @@
         <v>28.16</v>
       </c>
       <c r="BA12" t="n">
-        <v>28.31</v>
+        <v>28.29</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
+          <t>28.44</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>87.34</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>-112.56</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2025/12/22</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>815.5786516853932</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BK12" t="n">
+        <v>178.6</v>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>282.425</t>
+        </is>
+      </c>
+      <c r="BM12" t="n">
+        <v>243.94</v>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-103</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>6.738180950654459</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-14.37909705929633</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
           <t>28.45</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>72.12</t>
-        </is>
-      </c>
-      <c r="BD12" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-115.30</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2025/12/22</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>815.5786516853932</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BK12" t="n">
-        <v>264.2</v>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>330.125</t>
-        </is>
-      </c>
-      <c r="BM12" t="n">
-        <v>252.14</v>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-65</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>10.57768604337278</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>5.263711495227881</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>242.0</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
       <c r="BT12" t="inlineStr">
         <is>
           <t>2025/11/07</t>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-19.97</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -6501,7 +6501,7 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -6544,7 +6544,7 @@
         <v>28.16</v>
       </c>
       <c r="BA13" t="n">
-        <v>28.32</v>
+        <v>28.31</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
@@ -6553,14 +6553,14 @@
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>57.81</t>
+          <t>72.12</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-118.06</t>
+          <t>-115.30</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6588,34 +6588,34 @@
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>318.2</v>
+        <v>264.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>317.125</t>
+          <t>330.125</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>252.51</v>
+        <v>252.14</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-65</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>11.54386323394459</t>
+          <t>10.57768604337278</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>10.20830544829005</t>
+          <t>5.263711495227881</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
@@ -6782,7 +6782,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -6988,7 +6988,7 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -7007,14 +7007,14 @@
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.21</v>
+        <v>0.5</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -7024,30 +7024,30 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="AZ14" t="n">
         <v>28.16</v>
       </c>
       <c r="BA14" t="n">
-        <v>28.33</v>
+        <v>28.32</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>57.81</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-118.06</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7075,34 +7075,34 @@
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>263</v>
+        <v>318.2</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>340.225</t>
+          <t>317.125</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>254.55</v>
+        <v>252.51</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>11.78669192224541</t>
+          <t>11.54386323394459</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>7.264571615225691</t>
+          <t>10.20830544829005</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>263.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7167,12 +7167,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,7 +7475,7 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -7494,31 +7494,31 @@
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>1.14</v>
+        <v>0.71</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.52</v>
+        <v>-0.21</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>28.12</v>
+        <v>28.16</v>
       </c>
       <c r="BA15" t="n">
-        <v>28.36</v>
+        <v>28.33</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
@@ -7527,14 +7527,14 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>25.99</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-122.89</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7558,38 +7558,38 @@
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>328.6</v>
+        <v>263</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>322.425</t>
+          <t>340.225</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>249.89</v>
+        <v>254.55</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-77</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>12.60889561443081</t>
+          <t>11.78669192224541</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>10.19264572458985</t>
+          <t>7.264571615225691</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>263.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
@@ -7719,17 +7719,17 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,7 +7962,7 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7977,48 +7977,48 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0.8</v>
+        <v>-0.52</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="AZ16" t="n">
         <v>28.12</v>
       </c>
       <c r="BA16" t="n">
-        <v>28.37</v>
+        <v>28.36</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>25.99</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BE16" t="n">
         <v>-0.1</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-122.89</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8045,38 +8045,38 @@
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>386.25</v>
+        <v>328.6</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>336.525</t>
+          <t>322.425</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>259.19</v>
+        <v>249.89</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>13.04821377622008</t>
+          <t>12.60889561443081</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>39.19015710494619</t>
+          <t>10.19264572458985</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>456.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
@@ -8243,7 +8243,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>33.52</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,7 +8449,7 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -8464,28 +8464,28 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AV17" t="n">
-        <v>-1.08</v>
+        <v>-0.8</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
@@ -8496,16 +8496,16 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-25.75</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="BE17" t="n">
         <v>-0.1</v>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-124.65</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8532,38 +8532,38 @@
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>512.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>396.05</v>
+        <v>386.25</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>296.625</t>
+          <t>336.525</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>251.79</v>
+        <v>259.19</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>49</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>8.29513317099715</t>
+          <t>13.04821377622008</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>33.35838203742151</t>
+          <t>39.19015710494619</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>512.0</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
@@ -8693,17 +8693,17 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
+          <t>28.35</t>
+        </is>
+      </c>
+      <c r="CS17" t="inlineStr">
+        <is>
           <t>28.3</t>
-        </is>
-      </c>
-      <c r="CS17" t="inlineStr">
-        <is>
-          <t>28.0</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>25.90</t>
+          <t>33.52</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-15.74</t>
+          <t>-12.65</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,7 +8936,7 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -8946,28 +8946,28 @@
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AV18" t="n">
-        <v>-1.11</v>
+        <v>-1.08</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -8976,10 +8976,10 @@
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>28.13</v>
+        <v>28.12</v>
       </c>
       <c r="BA18" t="n">
-        <v>28.38</v>
+        <v>28.37</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
@@ -8988,11 +8988,11 @@
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-75.27</t>
+          <t>-25.75</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.17</v>
+        <v>-0.13</v>
       </c>
       <c r="BE18" t="n">
         <v>-0.1</v>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-123.06</t>
+          <t>-124.65</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9019,38 +9019,38 @@
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>512.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>316.05</v>
+        <v>396.05</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>251.025</t>
+          <t>296.625</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>242.12</v>
+        <v>251.79</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>99</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>3.738178831647267</t>
+          <t>8.29513317099715</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>17.83590401104965</t>
+          <t>33.35838203742151</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>512.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,17 +9115,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>68.17</t>
+          <t>25.90</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.51</t>
+          <t>-15.74</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,7 +9423,7 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -9442,47 +9442,47 @@
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-1.14</v>
+        <v>-1.87</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.49</v>
+        <v>-1.11</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>28.16</v>
+        <v>28.13</v>
       </c>
       <c r="BA19" t="n">
-        <v>28.4</v>
+        <v>28.38</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-46.29</t>
+          <t>-75.27</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.11</v>
+        <v>-0.17</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-118.72</t>
+          <t>-123.06</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9506,38 +9506,38 @@
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>591.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>417.45</v>
+        <v>316.05</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>248.225</t>
+          <t>251.025</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>241.58</v>
+        <v>242.12</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>1.174956071755924</t>
+          <t>3.738178831647267</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>43.88108168726677</t>
+          <t>17.83590401104965</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>591.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,164 +9714,164 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>-0.71</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>27.7</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>68.17</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2024-11-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2024-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>32.65</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>32.4</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>32.95</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-14.51</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
         <is>
           <t>27.9</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>60.51</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2024-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2024-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>32.4</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>-13.89</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
       <c r="AI20" t="inlineStr">
         <is>
           <t>2025/11/26</t>
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,7 +9910,7 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -9925,14 +9925,14 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-0.85</v>
+        <v>-1.14</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0.12</v>
+        <v>-0.49</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
@@ -9941,36 +9941,36 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>28.17</v>
+        <v>28.16</v>
       </c>
       <c r="BA20" t="n">
-        <v>28.41</v>
+        <v>28.4</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-21.70</t>
+          <t>-46.29</t>
         </is>
       </c>
       <c r="BD20" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="BE20" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BE20" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
       <c r="BF20" t="inlineStr">
         <is>
           <t>0.42</t>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-116.56</t>
+          <t>-118.72</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9993,38 +9993,38 @@
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>591.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>316.25</v>
+        <v>417.45</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>197.025</t>
+          <t>248.225</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>230.32</v>
+        <v>241.58</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>169</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-6.589794040155141</t>
+          <t>1.174956071755924</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>22.19986830731742</t>
+          <t>43.88108168726677</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>316.25</t>
+          <t>591.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10191,7 +10191,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10231,12 +10231,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>62.31</t>
+          <t>60.51</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,7 +10397,7 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -10412,18 +10412,18 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-1.13</v>
+        <v>-0.85</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.15</v>
+        <v>-0.12</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -10433,27 +10433,27 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>28.22</t>
+          <t>28.14</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>28.18</v>
+        <v>28.17</v>
       </c>
       <c r="BA21" t="n">
-        <v>28.42</v>
+        <v>28.41</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>28.52</t>
+          <t>28.51</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-21.70</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="BE21" t="n">
         <v>-0.07000000000000001</v>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-115.66</t>
+          <t>-116.56</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10480,38 +10480,38 @@
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>505.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>286.8</v>
+        <v>316.25</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>176.7</t>
+          <t>197.025</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>224.76</v>
+        <v>230.32</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>119</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-11.82427810333197</t>
+          <t>-6.589794040155141</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>19.87135389641412</t>
+          <t>22.19986830731742</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>505.0</t>
+          <t>316.25</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
@@ -10641,17 +10641,17 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
@@ -10678,7 +10678,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>201436.815</t>
+          <t>70250.984</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10718,12 +10718,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>51.75</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,87 +10863,87 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>56.96</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-7.43</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1,600</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>201437</t>
+          <t>70251</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>56.96</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>87.64</t>
+          <t>76.07</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>1.96</v>
+        <v>-0.59</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.55</v>
+        <v>4.01</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>31.68</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>30.59</v>
+        <v>30.71</v>
       </c>
       <c r="BA22" t="n">
-        <v>30.26</v>
+        <v>30.31</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>76.40</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-84.73</t>
+          <t>-82.29</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,48 +10962,48 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>1717531030.886963</t>
+          <t>1719783968.540859</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>6678368784.0</t>
+          <t>2229434678.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>4210288560.2</v>
+        <v>4389026707.8</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>2893256394.5</t>
+          <t>2892223299.6</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>2808126948.8</v>
+        <v>2780910122.44</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>1317032165</t>
+          <t>1496803408</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>67944137.9742843</t>
+          <t>127502634.1471599</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>657522973.3642759</t>
+          <t>455074363.0979757</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>6678368784.0</t>
+          <t>2229434678.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11068,17 +11068,17 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>88.19</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>143132</t>
+          <t>140695</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>201756.824</t>
+          <t>201436.815</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>45.52</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>56.96</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-7.43</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1,600</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>201437</t>
+          <t>70251</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.25</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>79.17</t>
+          <t>87.64</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>7.21</v>
+        <v>1.96</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.68</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>30.45</v>
+        <v>30.59</v>
       </c>
       <c r="BA23" t="n">
-        <v>30.21</v>
+        <v>30.26</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>87.50</t>
+          <t>76.40</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-87.65</t>
+          <t>-84.73</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,48 +11449,48 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>1717531030.886963</t>
+          <t>1719783968.540859</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>6703778205.0</t>
+          <t>6678368784.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>3070110512.8</v>
+        <v>4210288560.2</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>2633033521.2</t>
+          <t>2893256394.5</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>2766125687.26</v>
+        <v>2808126948.8</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>437076991</t>
+          <t>1317032165</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-39252013.91480508</t>
+          <t>67944137.9742843</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>446580799.0531235</t>
+          <t>657522973.3642759</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>6703778205.0</t>
+          <t>6678368784.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>88.19</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>143132</t>
+          <t>140695</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>173832.442</t>
+          <t>201756.824</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,177 +11677,177 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>33.45</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-5.35</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>16.60</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2025-12-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>31.65</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>-9.73</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>31.65</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>5.69</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
         <is>
           <t>2025-12-24 00:00:00</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2025-12-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>2025-12-24 00:00:00</t>
-        </is>
-      </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,67 +11858,67 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>1,600</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>201437</t>
+          <t>70251</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>59.72</t>
+          <t>79.17</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>4.08</v>
+        <v>7.21</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.45</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>7.40</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>30.24</v>
+        <v>30.45</v>
       </c>
       <c r="BA24" t="n">
-        <v>30.08</v>
+        <v>30.21</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>28.01</t>
+          <t>28.14</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>87.50</t>
         </is>
       </c>
       <c r="BD24" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BE24" t="n">
         <v>0.25</v>
       </c>
-      <c r="BE24" t="n">
-        <v>0.2</v>
-      </c>
       <c r="BF24" t="inlineStr">
         <is>
           <t>2.05</t>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-90.35</t>
+          <t>-87.65</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,48 +11936,48 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>1717531030.886963</t>
+          <t>1719783968.540859</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>5573788437.0</t>
+          <t>6703778205.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>1865132854</v>
+        <v>3070110512.8</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>2066069442.4</t>
+          <t>2633033521.2</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>2676628654.12</v>
+        <v>2766125687.26</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>-200936588</t>
+          <t>437076991</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>-127585252.6362467</t>
+          <t>-39252013.91480508</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>126563083.5352938</t>
+          <t>446580799.0531235</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>5573788437.0</t>
+          <t>6703778205.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,22 +12037,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>88.19</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>143132</t>
+          <t>140695</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>32.45</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12139,7 +12139,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>24919.15</t>
+          <t>173832.442</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,22 +12174,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-33.78</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,87 +12324,87 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>1,600</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>201437</t>
+          <t>70251</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>35.42</t>
+          <t>59.72</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>1.63</v>
+        <v>4.08</v>
       </c>
       <c r="AV25" t="n">
-        <v>-0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>7.40</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>30.1</v>
+        <v>30.24</v>
       </c>
       <c r="BA25" t="n">
-        <v>30.01</v>
+        <v>30.08</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-91.01</t>
+          <t>-90.35</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,48 +12423,48 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>1717531030.886963</t>
+          <t>1719783968.540859</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>759763435.0</t>
+          <t>5573788437.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>1077793893.4</v>
+        <v>1865132854</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>1627503444.5</t>
+          <t>2066069442.4</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>2702285145.58</v>
+        <v>2676628654.12</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>-549709551</t>
+          <t>-200936588</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-173794041.0310722</t>
+          <t>-127585252.6362467</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-214054859.3307233</t>
+          <t>126563083.5352938</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>759763435.0</t>
+          <t>5573788437.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,22 +12524,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>88.19</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>143132</t>
+          <t>140695</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>43906.141</t>
+          <t>24919.15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-17.87</t>
+          <t>-33.78</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,66 +12832,66 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>1,600</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>201437</t>
+          <t>70251</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="AV26" t="n">
-        <v>-0.65</v>
+        <v>-0.14</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>30.04</v>
+        <v>30.1</v>
       </c>
       <c r="BA26" t="n">
-        <v>30.02</v>
+        <v>30.01</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-36.09</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-90.57</t>
+          <t>-91.01</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>1717531030.886963</t>
+          <t>1719783968.540859</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>1335743940.0</t>
+          <t>759763435.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>1395419891.4</v>
+        <v>1077793893.4</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>1699043008.9</t>
+          <t>1627503444.5</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>2792941015.34</v>
+        <v>2702285145.58</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-303623117</t>
+          <t>-549709551</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>-166473892.2493175</t>
+          <t>-173794041.0310722</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-177218711.0917931</t>
+          <t>-214054859.3307233</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>1335743940.0</t>
+          <t>759763435.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>88.19</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>143132</t>
+          <t>140695</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
@@ -13086,12 +13086,12 @@
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13113,7 +13113,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>32757.289</t>
+          <t>43906.141</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-17.87</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>1,600</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>201437</t>
+          <t>70251</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>-0.1</v>
+        <v>2.04</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.08</v>
+        <v>-0.65</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>8.41</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>29.93</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>29.96</v>
+        <v>30.04</v>
       </c>
       <c r="BA27" t="n">
-        <v>30.05</v>
+        <v>30.02</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>27.72</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-51.90</t>
+          <t>-36.09</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-89.71</t>
+          <t>-90.57</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>1717531030.886963</t>
+          <t>1719783968.540859</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>977478547.0</t>
+          <t>1335743940.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>1576224228.8</v>
+        <v>1395419891.4</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>1778829403.7</t>
+          <t>1699043008.9</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>2993188486.96</v>
+        <v>2792941015.34</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-202605174</t>
+          <t>-303623117</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-164520288.8234128</t>
+          <t>-166473892.2493175</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-179978599.4614716</t>
+          <t>-177218711.0917931</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>977478547.0</t>
+          <t>1335743940.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,22 +13498,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>88.19</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>143132</t>
+          <t>140695</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>22912.409</t>
+          <t>32757.289</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,177 +13625,177 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>29.9</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-11.39</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2025-12-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>31.65</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>8.67</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>22.49</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="AK28" t="inlineStr">
         <is>
           <t>2025-12-24 00:00:00</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2025-12-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>2025-12-24 00:00:00</t>
-        </is>
-      </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,66 +13806,66 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>1,600</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>201437</t>
+          <t>70251</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>-2.7</v>
+        <v>-0.1</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.48</v>
+        <v>-0.08</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>8.41</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>29.93</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>29.88</v>
+        <v>29.96</v>
       </c>
       <c r="BA28" t="n">
         <v>30.05</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>27.64</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-46.45</t>
+          <t>-51.90</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="BE28" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-88.38</t>
+          <t>-89.71</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>1717531030.886963</t>
+          <t>1719783968.540859</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>678889911.0</t>
+          <t>977478547.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>2195956529.6</v>
+        <v>1576224228.8</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>1792692633.0</t>
+          <t>1778829403.7</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>3146696765.1</v>
+        <v>2993188486.96</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>403263896</t>
+          <t>-202605174</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-161709686.8892204</t>
+          <t>-164520288.8234128</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-139107912.1873884</t>
+          <t>-179978599.4614716</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>678889911.0</t>
+          <t>977478547.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,22 +13985,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>88.19</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>143132</t>
+          <t>140695</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
+          <t>29.8</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>30.1</t>
+        </is>
+      </c>
+      <c r="CS28" t="inlineStr">
+        <is>
           <t>29.6</t>
         </is>
       </c>
-      <c r="CR28" t="inlineStr">
-        <is>
-          <t>29.95</t>
-        </is>
-      </c>
-      <c r="CS28" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>54441.068</t>
+          <t>22912.409</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -14222,7 +14222,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -14272,17 +14272,17 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -14293,38 +14293,38 @@
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>1,600</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>201437</t>
+          <t>70251</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AU29" t="n">
-        <v>-1.39</v>
+        <v>-2.7</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -14336,23 +14336,23 @@
         <v>29.88</v>
       </c>
       <c r="BA29" t="n">
-        <v>30.02</v>
+        <v>30.05</v>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>27.64</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-24.87</t>
+          <t>-46.45</t>
         </is>
       </c>
       <c r="BD29" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="BE29" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>-87.03</t>
+          <t>-88.38</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
@@ -14371,43 +14371,43 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>1717531030.886963</t>
+          <t>1719783968.540859</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
         <is>
-          <t>1637093634.0</t>
+          <t>678889911.0</t>
         </is>
       </c>
       <c r="BK29" t="n">
-        <v>2267006030.8</v>
+        <v>2195956529.6</v>
       </c>
       <c r="BL29" t="inlineStr">
         <is>
-          <t>1933953822.0</t>
+          <t>1792692633.0</t>
         </is>
       </c>
       <c r="BM29" t="n">
-        <v>3226284926.5</v>
+        <v>3146696765.1</v>
       </c>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>333052208</t>
+          <t>403263896</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>-165819100.4713716</t>
+          <t>-161709686.8892204</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>-43761436.78914857</t>
+          <t>-139107912.1873884</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>1637093634.0</t>
+          <t>678889911.0</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="BU29" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="BV29" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="CI29" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>88.19</t>
         </is>
       </c>
       <c r="CJ29" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
         <is>
-          <t>143132</t>
+          <t>140695</t>
         </is>
       </c>
       <c r="CN29" t="inlineStr">
@@ -14537,22 +14537,22 @@
       </c>
       <c r="CQ29" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CR29" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CT29" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CU29" t="inlineStr">
@@ -14584,12 +14584,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>78847.301</t>
+          <t>54441.068</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -14599,177 +14599,177 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>29.9</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>17.22</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2025-12-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>31.65</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
           <t>29.45</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>8.82</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>13.67</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
         <is>
           <t>2025-12-24 00:00:00</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2025-12-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>-7.54</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>2025-12-24 00:00:00</t>
-        </is>
-      </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -14780,38 +14780,38 @@
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>1,600</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>201437</t>
+          <t>70251</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>53.19</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="AU30" t="n">
-        <v>-2.87</v>
+        <v>-1.39</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -14820,26 +14820,26 @@
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>29.84</v>
+        <v>29.88</v>
       </c>
       <c r="BA30" t="n">
-        <v>29.92</v>
+        <v>30.02</v>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-12.08</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="BD30" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>-86.22</t>
+          <t>-87.03</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -14858,48 +14858,48 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>1717531030.886963</t>
+          <t>1719783968.540859</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
-          <t>2347893425.0</t>
+          <t>1637093634.0</t>
         </is>
       </c>
       <c r="BK30" t="n">
-        <v>2177212995.6</v>
+        <v>2267006030.8</v>
       </c>
       <c r="BL30" t="inlineStr">
         <is>
-          <t>1915411140.1</t>
+          <t>1933953822.0</t>
         </is>
       </c>
       <c r="BM30" t="n">
-        <v>3205376660.36</v>
+        <v>3226284926.5</v>
       </c>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>261801855</t>
+          <t>333052208</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>-188011402.9590485</t>
+          <t>-165819100.4713716</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>-8653962.37062192</t>
+          <t>-43761436.78914857</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>2347893425.0</t>
+          <t>1637093634.0</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="BU30" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="BV30" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="CI30" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>88.19</t>
         </is>
       </c>
       <c r="CJ30" t="inlineStr">
@@ -14999,12 +14999,12 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
         <is>
-          <t>143132</t>
+          <t>140695</t>
         </is>
       </c>
       <c r="CN30" t="inlineStr">
@@ -15024,22 +15024,22 @@
       </c>
       <c r="CQ30" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CR30" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CT30" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CU30" t="inlineStr">
@@ -15061,7 +15061,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -15071,12 +15071,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>71652.364</t>
+          <t>78847.301</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -15096,17 +15096,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-12-31 00:00:00</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -15246,17 +15246,17 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -15267,66 +15267,66 @@
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>1,600</t>
+          <t>680</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>201437</t>
+          <t>70251</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>59.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>53.19</t>
         </is>
       </c>
       <c r="AU31" t="n">
-        <v>1.08</v>
+        <v>-2.87</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>29.89</v>
+        <v>29.84</v>
       </c>
       <c r="BA31" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>21.13</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="BD31" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="BE31" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-86.22</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
@@ -15345,43 +15345,43 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>1717531030.886963</t>
+          <t>1719783968.540859</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
         <is>
-          <t>2239765627.0</t>
+          <t>2347893425.0</t>
         </is>
       </c>
       <c r="BK31" t="n">
-        <v>2002666126.4</v>
+        <v>2177212995.6</v>
       </c>
       <c r="BL31" t="inlineStr">
         <is>
-          <t>1855304078.9</t>
+          <t>1915411140.1</t>
         </is>
       </c>
       <c r="BM31" t="n">
-        <v>3181037509.62</v>
+        <v>3205376660.36</v>
       </c>
       <c r="BN31" t="inlineStr">
         <is>
-          <t>147362047</t>
+          <t>261801855</t>
         </is>
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>-220621846.7023988</t>
+          <t>-188011402.9590485</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>-34348477.86663342</t>
+          <t>-8653962.37062192</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>2239765627.0</t>
+          <t>2347893425.0</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="BU31" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="BV31" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
@@ -15456,12 +15456,12 @@
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -15471,7 +15471,7 @@
       </c>
       <c r="CI31" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>88.19</t>
         </is>
       </c>
       <c r="CJ31" t="inlineStr">
@@ -15486,12 +15486,12 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
         <is>
-          <t>143132</t>
+          <t>140695</t>
         </is>
       </c>
       <c r="CN31" t="inlineStr">
@@ -15511,22 +15511,22 @@
       </c>
       <c r="CQ31" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CR31" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CT31" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CU31" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼胚.xlsx
+++ b/Result/checksun_type/不鏽鋼胚.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5123.0</t>
+          <t>2495.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-31.53</t>
+          <t>-33.16</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,66 +1144,66 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>54.29</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>3.88</v>
+        <v>1.05</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.31</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>31.67</v>
+        <v>31.76</v>
       </c>
       <c r="BA2" t="n">
-        <v>32.1</v>
+        <v>32.08</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>33.46</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>239.41</t>
+          <t>543.24</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-105.48</t>
+          <t>-102.32</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>305846.0409836065</t>
+          <t>305473.1165644172</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>169023.0</t>
+          <t>82324.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>74997.39999999999</v>
+        <v>82989.8</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>78680.3</t>
+          <t>81392.6</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>75523.48</v>
+        <v>75011.82000000001</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-3682</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>1876.033937618166</t>
+          <t>2509.178445454278</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>7080.697192886437</t>
+          <t>5991.473238552891</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>169023.0</t>
+          <t>82324.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>18.58</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>5123.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-21.19</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-34.80</t>
+          <t>-31.53</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,66 +1631,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.25</v>
+        <v>3.88</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.2</v>
+        <v>1.68</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>31.93</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>31.55</v>
+        <v>31.67</v>
       </c>
       <c r="BA3" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>33.46</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>239.41</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.02</v>
+        <v>0.11</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-108.76</t>
+          <t>-105.48</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>305846.0409836065</t>
+          <t>305473.1165644172</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>62765.0</t>
+          <t>169023.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>53719</v>
+        <v>74997.39999999999</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>68161.9</t>
+          <t>78680.3</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>74650.12</v>
+        <v>75523.48</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-14442</t>
+          <t>-3682</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>929.7315275693895</t>
+          <t>1876.033937618166</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-905.3292006687407</t>
+          <t>7080.697192886437</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>62765.0</t>
+          <t>169023.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-14.84</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>18.58</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1650.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-21.19</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-35.11</t>
+          <t>-34.80</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-1.03</v>
+        <v>-0.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.61</v>
+        <v>1.2</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>31.93</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>31.52</v>
+        <v>31.55</v>
       </c>
       <c r="BA4" t="n">
-        <v>32.19</v>
+        <v>32.12</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>33.57</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>82.02</t>
+          <t>82.03</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-110.56</t>
+          <t>-108.76</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>305846.0409836065</t>
+          <t>305473.1165644172</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>52316.0</t>
+          <t>62765.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>72699</v>
+        <v>53719</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>71009.8</t>
+          <t>68161.9</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>75019.39999999999</v>
+        <v>74650.12</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>-14442</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>1263.378932703595</t>
+          <t>929.7315275693895</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-896.8194342951028</t>
+          <t>-905.3292006687407</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>52316.0</t>
+          <t>62765.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-15.24</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>18.58</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1515.0</t>
+          <t>1650.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-34.70</t>
+          <t>-35.11</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>74.32</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.09</v>
+        <v>1.61</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>31.5</v>
+        <v>31.52</v>
       </c>
       <c r="BA5" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>33.57</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>90.46</t>
+          <t>82.02</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.18</v>
+        <v>-0.15</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-112.72</t>
+          <t>-110.56</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>305846.0409836065</t>
+          <t>305473.1165644172</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>48521.0</t>
+          <t>52316.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>74898.8</v>
+        <v>72699</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>76512.7</t>
+          <t>71009.8</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>75902.94</v>
+        <v>75019.39999999999</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-1613</t>
+          <t>1689</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>1656.142272157904</t>
+          <t>1263.378932703595</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>266.9023546063399</t>
+          <t>-896.8194342951028</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>48521.0</t>
+          <t>52316.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-15.24</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>18.58</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1325.0</t>
+          <t>1515.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-34.29</t>
+          <t>-34.70</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,66 +3092,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>90.99</t>
+          <t>74.32</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.22</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>32.16</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>31.48</v>
+        <v>31.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>32.36</v>
+        <v>32.28</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.46</t>
         </is>
       </c>
       <c r="BD6" t="n">
         <v>-0.02</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.22</v>
+        <v>-0.18</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-115.60</t>
+          <t>-112.72</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>305846.0409836065</t>
+          <t>305473.1165644172</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>42362.0</t>
+          <t>48521.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>79795.39999999999</v>
+        <v>74898.8</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>75614.5</t>
+          <t>76512.7</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>75871.44</v>
+        <v>75902.94</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>-1613</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>1908.73134807637</t>
+          <t>1656.142272157904</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>2326.43696894389</t>
+          <t>266.9023546063399</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>42362.0</t>
+          <t>48521.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-14.17</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>18.58</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1966.0</t>
+          <t>1325.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,12 +3579,12 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3594,51 +3594,51 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>90.99</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.03</v>
+        <v>-0.22</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>32.17</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>31.45</v>
+        <v>31.48</v>
       </c>
       <c r="BA7" t="n">
-        <v>32.44</v>
+        <v>32.36</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>33.79</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>79.88</t>
+          <t>88.78</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.27</v>
+        <v>-0.22</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-119.06</t>
+          <t>-115.60</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>305846.0409836065</t>
+          <t>305473.1165644172</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>62631.0</t>
+          <t>42362.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>82363.2</v>
+        <v>79795.39999999999</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>77673.9</t>
+          <t>75614.5</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>75816.44</v>
+        <v>75871.44</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>1832.784871555003</t>
+          <t>1908.73134807637</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>5845.435097678099</t>
+          <t>2326.43696894389</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>62631.0</t>
+          <t>42362.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>18.58</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4838.0</t>
+          <t>1966.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-33.78</t>
+          <t>-34.29</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>23.83</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>31.44</v>
+        <v>31.45</v>
       </c>
       <c r="BA8" t="n">
-        <v>32.52</v>
+        <v>32.44</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>33.79</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>71.83</t>
+          <t>79.88</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.33</v>
+        <v>-0.27</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-122.87</t>
+          <t>-119.06</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>305846.0409836065</t>
+          <t>305473.1165644172</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>157665.0</t>
+          <t>62631.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>82604.8</v>
+        <v>82363.2</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>76417.1</t>
+          <t>77673.9</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>75403.94</v>
+        <v>75816.44</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>1103.212103168985</t>
+          <t>1832.784871555003</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>8492.13117095278</t>
+          <t>5845.435097678099</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>157665.0</t>
+          <t>62631.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-14.17</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>18.58</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1961.0</t>
+          <t>4838.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>8.10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>23.83</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,12 +4553,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4572,47 +4572,47 @@
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>1.51</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>31.41</v>
+        <v>31.44</v>
       </c>
       <c r="BA9" t="n">
-        <v>32.59</v>
+        <v>32.52</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>33.91</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>57.53</t>
+          <t>71.83</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.16</v>
+        <v>-0.09</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.38</v>
+        <v>-0.33</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-126.97</t>
+          <t>-122.87</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>305846.0409836065</t>
+          <t>305473.1165644172</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>63315.0</t>
+          <t>157665.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>69320.60000000001</v>
+        <v>82604.8</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>65444.2</t>
+          <t>76417.1</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>73402.25999999999</v>
+        <v>75403.94</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-240.2277273371592</t>
+          <t>1103.212103168985</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>1787.620876668276</t>
+          <t>8492.13117095278</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>63315.0</t>
+          <t>157665.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>18.58</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,17 +4797,17 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2278.0</t>
+          <t>1961.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-34.60</t>
+          <t>-33.78</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,12 +5040,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5059,14 +5059,14 @@
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.35</v>
+        <v>1.47</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -5076,30 +5076,30 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>31.39</v>
+        <v>31.41</v>
       </c>
       <c r="BA10" t="n">
-        <v>32.66</v>
+        <v>32.59</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>33.91</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>57.53</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.25</v>
+        <v>-0.16</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.44</v>
+        <v>-0.38</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-130.85</t>
+          <t>-126.97</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>305846.0409836065</t>
+          <t>305473.1165644172</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>73004.0</t>
+          <t>63315.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>78126.60000000001</v>
+        <v>69320.60000000001</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>62199.4</t>
+          <t>65444.2</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>73508.56</v>
+        <v>73402.25999999999</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-608.9274735199656</t>
+          <t>-240.2277273371592</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>2254.833996380839</t>
+          <t>1787.620876668276</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>73004.0</t>
+          <t>63315.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-14.57</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>18.58</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
+          <t>32.2</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>32.45</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
           <t>31.9</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
-        <is>
-          <t>32.25</t>
-        </is>
-      </c>
-      <c r="CS10" t="inlineStr">
-        <is>
-          <t>31.75</t>
-        </is>
-      </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,74 +5346,74 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-40.21</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>29.2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>48.81</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>29.2</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>32.65</t>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,47 +5527,47 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-1.68</v>
+        <v>-1.91</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.1</v>
+        <v>2.82</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.36</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>28.53</v>
+        <v>28.56</v>
       </c>
       <c r="BA11" t="n">
         <v>28.38</v>
@@ -5579,14 +5579,14 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>73.81</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-42.82</t>
+          <t>-36.76</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,48 +5605,48 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>762.3757828810021</t>
+          <t>761.0531249999999</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>519.2</v>
+        <v>212</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>348.9</t>
+          <t>354.6</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>275.21</v>
+        <v>274.62</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>-142</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>23.61026875681522</t>
+          <t>17.75050913863461</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>6.250315824094628</t>
+          <t>-14.47816876135875</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,22 +5843,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>48.81</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>52.27</t>
+          <t>40.91</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-0.24</v>
+        <v>-1.68</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.67</v>
+        <v>4.1</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>28.48</v>
+        <v>28.53</v>
       </c>
       <c r="BA12" t="n">
-        <v>28.37</v>
+        <v>28.38</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>115.36</t>
+          <t>73.81</t>
         </is>
       </c>
       <c r="BD12" t="n">
         <v>0.32</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-53.37</t>
+          <t>-42.82</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,48 +6092,48 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>762.3757828810021</t>
+          <t>761.0531249999999</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>437.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>490.2</v>
+        <v>519.2</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>377.2</t>
+          <t>348.9</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>272.92</v>
+        <v>275.21</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>170</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>26.7666238354917</t>
+          <t>23.61026875681522</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>26.21063966673887</t>
+          <t>6.250315824094628</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>437.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>29.96</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,87 +6480,87 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>14.02</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>52.27</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-1.5</v>
+        <v>-0.24</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.09</v>
+        <v>3.67</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>28.41</v>
+        <v>28.48</v>
       </c>
       <c r="BA13" t="n">
-        <v>28.35</v>
+        <v>28.37</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>178.33</t>
+          <t>115.36</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-66.82</t>
+          <t>-53.37</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>762.3757828810021</t>
+          <t>761.0531249999999</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>437.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>451.2</v>
+        <v>490.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>384.7</t>
+          <t>377.2</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>265.32</v>
+        <v>272.92</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>113</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>26.86771186617403</t>
+          <t>26.7666238354917</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>25.50357945384718</t>
+          <t>26.21063966673887</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>437.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,17 +6680,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -6988,50 +6988,50 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>4.52</v>
+        <v>-1.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.82</v>
+        <v>3.09</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>28.38</v>
+        <v>28.41</v>
       </c>
       <c r="BA14" t="n">
-        <v>28.36</v>
+        <v>28.35</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
@@ -7040,14 +7040,14 @@
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>442.46</t>
+          <t>178.33</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-81.61</t>
+          <t>-66.82</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>762.3757828810021</t>
+          <t>761.0531249999999</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>336.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>511.8</v>
+        <v>451.2</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>387.4</t>
+          <t>384.7</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>273</v>
+        <v>265.32</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>66</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>27.11573594114255</t>
+          <t>26.86771186617403</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>67.29693702636456</t>
+          <t>25.50357945384718</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>336.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,17 +7167,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7269,7 +7269,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-5.9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,33 +7454,33 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>51.40</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -7494,47 +7494,47 @@
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>6.12</v>
+        <v>4.52</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.66</v>
+        <v>2.82</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>29.18</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>28.27</v>
+        <v>28.38</v>
       </c>
       <c r="BA15" t="n">
-        <v>28.33</v>
+        <v>28.36</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>2937.20</t>
+          <t>442.46</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-101.95</t>
+          <t>-81.61</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>762.3757828810021</t>
+          <t>761.0531249999999</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>1621.0</t>
+          <t>336.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>497.2</v>
+        <v>511.8</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>412.9</t>
+          <t>387.4</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>266.86</v>
+        <v>273</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>124</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>19.81006301655673</t>
+          <t>27.11573594114255</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>91.7054143790192</t>
+          <t>67.29693702636456</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>1621.0</t>
+          <t>336.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,139 +7781,139 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-5.9</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>20.42</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>32.65</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>32.4</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>-9.88</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
           <t>28.3</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>3.08</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-36.76</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>32.4</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>-9.88</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
       <c r="AG16" t="inlineStr">
         <is>
           <t>2025/12/16</t>
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.40</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,12 +7962,12 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7981,48 +7981,48 @@
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.51</v>
+        <v>1.66</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
           <t>-0.46</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>28.74</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>28.16</v>
+        <v>28.27</v>
       </c>
       <c r="BA16" t="n">
-        <v>28.29</v>
+        <v>28.33</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>2937.20</t>
         </is>
       </c>
       <c r="BD16" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BE16" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BE16" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="BF16" t="inlineStr">
         <is>
           <t>0.32</t>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-116.28</t>
+          <t>-101.95</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>762.3757828810021</t>
+          <t>761.0531249999999</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1621.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>178.6</v>
+        <v>497.2</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>282.425</t>
+          <t>412.9</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>243.94</v>
+        <v>266.86</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-103</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>6.738180950654459</t>
+          <t>19.81006301655673</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-14.37909705929633</t>
+          <t>91.7054143790192</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>1621.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,17 +8141,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-19.97</t>
+          <t>-36.76</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -8449,12 +8449,12 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -8471,16 +8471,16 @@
         <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
           <t>-0.53</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>-0.47</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -8492,23 +8492,23 @@
         <v>28.16</v>
       </c>
       <c r="BA17" t="n">
-        <v>28.31</v>
+        <v>28.29</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>72.12</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-119.84</t>
+          <t>-116.28</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>762.3757828810021</t>
+          <t>761.0531249999999</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -8536,34 +8536,34 @@
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>264.2</v>
+        <v>178.6</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>330.125</t>
+          <t>282.425</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>252.14</v>
+        <v>243.94</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-65</t>
+          <t>-103</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>10.57768604337278</t>
+          <t>6.738180950654459</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>5.263711495227881</t>
+          <t>-14.37909705929633</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-19.97</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -8936,12 +8936,12 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -8979,7 +8979,7 @@
         <v>28.16</v>
       </c>
       <c r="BA18" t="n">
-        <v>28.32</v>
+        <v>28.31</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
@@ -8988,14 +8988,14 @@
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>57.81</t>
+          <t>72.12</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-123.42</t>
+          <t>-119.84</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>762.3757828810021</t>
+          <t>761.0531249999999</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -9023,34 +9023,34 @@
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>318.2</v>
+        <v>264.2</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>317.125</t>
+          <t>330.125</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>252.51</v>
+        <v>252.14</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-65</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>11.54386323394459</t>
+          <t>10.57768604337278</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>10.20830544829005</t>
+          <t>5.263711495227881</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9217,7 +9217,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -9423,12 +9423,12 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9442,14 +9442,14 @@
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.21</v>
+        <v>0.5</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -9459,30 +9459,30 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
         <v>28.16</v>
       </c>
       <c r="BA19" t="n">
-        <v>28.33</v>
+        <v>28.32</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>57.81</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-126.80</t>
+          <t>-123.42</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>762.3757828810021</t>
+          <t>761.0531249999999</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -9510,34 +9510,34 @@
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>263</v>
+        <v>318.2</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>340.225</t>
+          <t>317.125</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>254.55</v>
+        <v>252.51</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>11.78669192224541</t>
+          <t>11.54386323394459</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>7.264571615225691</t>
+          <t>10.20830544829005</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>263.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>264591.244</t>
+          <t>195862.867</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>21.01</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>74.82</t>
+          <t>55.38</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1,077</t>
+          <t>990</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>264591</t>
+          <t>195863</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.91</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>13.94</v>
+        <v>6.09</v>
       </c>
       <c r="AV20" t="n">
-        <v>9.48</v>
+        <v>12.23</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>31.79</v>
+        <v>32.17</v>
       </c>
       <c r="BA20" t="n">
-        <v>30.79</v>
+        <v>30.93</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>29.34</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>79.03</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-50.31</t>
+          <t>-38.07</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,48 +9988,48 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>1480089801.70082</t>
+          <t>1500402533.868098</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>10237740986.0</t>
+          <t>7608677221.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>5594762063</v>
+        <v>6630219145.4</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>4991894385.4</t>
+          <t>5676785764.0</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>2978303860.6</v>
+        <v>3052834273.88</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>602867677</t>
+          <t>953433381</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>366759452.7992064</t>
+          <t>465422488.6070521</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>974988177.1639261</t>
+          <t>1008069185.550203</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>10237740986.0</t>
+          <t>7608677221.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>30.21</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -10089,22 +10089,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>110.14</t>
+          <t>106.39</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>175702</t>
+          <t>169720</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>217071.602</t>
+          <t>264591.244</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>25.28</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>61.38</t>
+          <t>74.82</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,12 +10397,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1,077</t>
+          <t>990</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>264591</t>
+          <t>195863</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10412,51 +10412,51 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>94.84</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>8.52</v>
+        <v>13.94</v>
       </c>
       <c r="AV21" t="n">
-        <v>5.92</v>
+        <v>9.48</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>33.22000000000001</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>31.36</v>
+        <v>31.79</v>
       </c>
       <c r="BA21" t="n">
-        <v>30.6</v>
+        <v>30.79</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>67.96</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>1.05</v>
+        <v>1.54</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.62</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-61.59</t>
+          <t>-50.31</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,48 +10475,48 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>1480089801.70082</t>
+          <t>1500402533.868098</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>7720798099.0</t>
+          <t>10237740986.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>3993100801.4</v>
+        <v>5594762063</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>4101694680.8</t>
+          <t>4991894385.4</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>2883137343.96</v>
+        <v>2978303860.6</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-108593879</t>
+          <t>602867677</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>256172412.005621</t>
+          <t>366759452.7992064</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>611223184.0348191</t>
+          <t>974988177.1639261</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>7720798099.0</t>
+          <t>10237740986.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>30.21</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>110.14</t>
+          <t>106.39</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>175702</t>
+          <t>169720</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>152715.387</t>
+          <t>217071.602</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>15.26</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>43.18</t>
+          <t>61.38</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,12 +10884,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1,077</t>
+          <t>990</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>264591</t>
+          <t>195863</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -10899,51 +10899,51 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>80.91</t>
+          <t>94.84</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>3.48</v>
+        <v>8.52</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.48</v>
+        <v>5.92</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>33.22000000000001</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>31.08</v>
+        <v>31.36</v>
       </c>
       <c r="BA22" t="n">
-        <v>30.47</v>
+        <v>30.6</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>48.81</t>
+          <t>67.96</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>0.77</v>
+        <v>1.05</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-68.12</t>
+          <t>-61.59</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,48 +10962,48 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>1480089801.70082</t>
+          <t>1500402533.868098</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>5199136194.0</t>
+          <t>7720798099.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>3784614938.4</v>
+        <v>3993100801.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>3427362725.6</t>
+          <t>4101694680.8</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>2765585656.86</v>
+        <v>2883137343.96</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>357252212</t>
+          <t>-108593879</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>191617726.1821304</t>
+          <t>256172412.005621</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>339401960.8848505</t>
+          <t>611223184.0348191</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>5199136194.0</t>
+          <t>7720798099.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>110.14</t>
+          <t>106.39</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>175702</t>
+          <t>169720</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>73283.072</t>
+          <t>152715.387</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>37.31</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>43.18</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1,077</t>
+          <t>990</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>264591</t>
+          <t>195863</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>84.51</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>66.57</t>
+          <t>80.91</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>1.42</v>
+        <v>3.48</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.88</v>
+        <v>4.48</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>30.93</v>
+        <v>31.08</v>
       </c>
       <c r="BA23" t="n">
-        <v>30.4</v>
+        <v>30.47</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>44.06</t>
+          <t>48.81</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>0.65</v>
+        <v>0.77</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-72.01</t>
+          <t>-68.12</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,48 +11449,48 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>1480089801.70082</t>
+          <t>1500402533.868098</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>2384743227.0</t>
+          <t>5199136194.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>4085543340.6</v>
+        <v>3784614938.4</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>2975338097.3</t>
+          <t>3427362725.6</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>2713094571.68</v>
+        <v>2765585656.86</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>1110205243</t>
+          <t>357252212</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>164747865.3270903</t>
+          <t>191617726.1821304</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>209142490.4604368</t>
+          <t>339401960.8848505</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>2384743227.0</t>
+          <t>5199136194.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>110.14</t>
+          <t>106.39</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>175702</t>
+          <t>169720</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>75139.115</t>
+          <t>73283.072</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>62.84</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,66 +11858,66 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>1,077</t>
+          <t>990</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>264591</t>
+          <t>195863</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>58.23</t>
+          <t>84.51</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>62.15</t>
+          <t>66.57</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>-1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AV24" t="n">
-        <v>4.5</v>
+        <v>4.88</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>30.8</v>
+        <v>30.93</v>
       </c>
       <c r="BA24" t="n">
-        <v>30.34</v>
+        <v>30.4</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>28.62</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>44.06</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-75.09</t>
+          <t>-72.01</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,48 +11936,48 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>1480089801.70082</t>
+          <t>1500402533.868098</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>2431391809.0</t>
+          <t>2384743227.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>4723352382.6</v>
+        <v>4085543340.6</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>2900573138.0</t>
+          <t>2975338097.3</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>2734281368.9</v>
+        <v>2713094571.68</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>1822779244</t>
+          <t>1110205243</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>156676115.3028455</t>
+          <t>164747865.3270903</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>317130261.6591163</t>
+          <t>209142490.4604368</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>2431391809.0</t>
+          <t>2384743227.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12037,22 +12037,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>110.14</t>
+          <t>106.39</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>175702</t>
+          <t>169720</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>70250.984</t>
+          <t>75139.115</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>51.75</t>
+          <t>62.84</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,203 +12345,203 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>1,077</t>
+          <t>990</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>264591</t>
+          <t>195863</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>56.96</t>
+          <t>58.23</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>76.07</t>
+          <t>62.15</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-0.59</v>
+        <v>-1.21</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>6.40</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>32.19</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>28.51</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>40.69</t>
+        </is>
+      </c>
+      <c r="BD25" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>-75.09</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2025/12/24</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>1500402533.868098</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>2431391809.0</t>
+        </is>
+      </c>
+      <c r="BK25" t="n">
+        <v>4723352382.6</v>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>2900573138.0</t>
+        </is>
+      </c>
+      <c r="BM25" t="n">
+        <v>2734281368.9</v>
+      </c>
+      <c r="BN25" t="inlineStr">
+        <is>
+          <t>1822779244</t>
+        </is>
+      </c>
+      <c r="BO25" t="inlineStr">
+        <is>
+          <t>156676115.3028455</t>
+        </is>
+      </c>
+      <c r="BP25" t="inlineStr">
+        <is>
+          <t>317130261.6591163</t>
+        </is>
+      </c>
+      <c r="BQ25" t="inlineStr">
+        <is>
+          <t>2431391809.0</t>
+        </is>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="BS25" t="inlineStr">
+        <is>
+          <t>30.45</t>
+        </is>
+      </c>
+      <c r="BT25" t="inlineStr">
+        <is>
+          <t>2025/12/22</t>
+        </is>
+      </c>
+      <c r="BU25" t="inlineStr">
+        <is>
+          <t>4.43</t>
+        </is>
+      </c>
+      <c r="BV25" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BW25" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BX25" t="inlineStr">
+        <is>
+          <t>電器電纜</t>
+        </is>
+      </c>
+      <c r="BY25" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ25" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="CA25" t="inlineStr">
+        <is>
+          <t>-6.059105961166755</t>
+        </is>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>-29.72089430657912</t>
+        </is>
+      </c>
+      <c r="CC25" t="inlineStr">
+        <is>
+          <t>-4.098016323960095</t>
+        </is>
+      </c>
+      <c r="CD25" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE25" t="inlineStr">
+        <is>
+          <t>價跌量縮</t>
+        </is>
+      </c>
+      <c r="CF25" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="CG25" t="inlineStr">
+        <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>6.78</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>31.94</t>
-        </is>
-      </c>
-      <c r="AZ25" t="n">
-        <v>30.71</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>30.31</v>
-      </c>
-      <c r="BB25" t="inlineStr">
-        <is>
-          <t>28.39</t>
-        </is>
-      </c>
-      <c r="BC25" t="inlineStr">
-        <is>
-          <t>55.02</t>
-        </is>
-      </c>
-      <c r="BD25" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BF25" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="BG25" t="inlineStr">
-        <is>
-          <t>-77.63</t>
-        </is>
-      </c>
-      <c r="BH25" t="inlineStr">
-        <is>
-          <t>2025/12/24</t>
-        </is>
-      </c>
-      <c r="BI25" t="inlineStr">
-        <is>
-          <t>1480089801.70082</t>
-        </is>
-      </c>
-      <c r="BJ25" t="inlineStr">
-        <is>
-          <t>2229434678.0</t>
-        </is>
-      </c>
-      <c r="BK25" t="n">
-        <v>4389026707.8</v>
-      </c>
-      <c r="BL25" t="inlineStr">
-        <is>
-          <t>2892223299.6</t>
-        </is>
-      </c>
-      <c r="BM25" t="n">
-        <v>2780910122.44</v>
-      </c>
-      <c r="BN25" t="inlineStr">
-        <is>
-          <t>1496803408</t>
-        </is>
-      </c>
-      <c r="BO25" t="inlineStr">
-        <is>
-          <t>127502634.1471599</t>
-        </is>
-      </c>
-      <c r="BP25" t="inlineStr">
-        <is>
-          <t>455074363.0979757</t>
-        </is>
-      </c>
-      <c r="BQ25" t="inlineStr">
-        <is>
-          <t>2229434678.0</t>
-        </is>
-      </c>
-      <c r="BR25" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="BS25" t="inlineStr">
-        <is>
-          <t>30.45</t>
-        </is>
-      </c>
-      <c r="BT25" t="inlineStr">
-        <is>
-          <t>2025/12/22</t>
-        </is>
-      </c>
-      <c r="BU25" t="inlineStr">
-        <is>
-          <t>4.27</t>
-        </is>
-      </c>
-      <c r="BV25" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BW25" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BX25" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BY25" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ25" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="CA25" t="inlineStr">
-        <is>
-          <t>-6.059105961166755</t>
-        </is>
-      </c>
-      <c r="CB25" t="inlineStr">
-        <is>
-          <t>-29.72089430657912</t>
-        </is>
-      </c>
-      <c r="CC25" t="inlineStr">
-        <is>
-          <t>-4.098016323960095</t>
-        </is>
-      </c>
-      <c r="CD25" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE25" t="inlineStr">
-        <is>
-          <t>價跌量縮</t>
-        </is>
-      </c>
-      <c r="CF25" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
-      <c r="CG25" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
       <c r="CH25" t="inlineStr">
         <is>
           <t>9.28</t>
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>110.14</t>
+          <t>106.39</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>175702</t>
+          <t>169720</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>201436.815</t>
+          <t>70250.984</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>51.75</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,87 +12811,87 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>56.96</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-7.43</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>1,077</t>
+          <t>990</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>264591</t>
+          <t>195863</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>56.96</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>87.64</t>
+          <t>76.07</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>1.96</v>
+        <v>-0.59</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.55</v>
+        <v>4.01</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>31.68</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>30.59</v>
+        <v>30.71</v>
       </c>
       <c r="BA26" t="n">
-        <v>30.26</v>
+        <v>30.31</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>76.40</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-80.70</t>
+          <t>-77.63</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,48 +12910,48 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>1480089801.70082</t>
+          <t>1500402533.868098</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>6678368784.0</t>
+          <t>2229434678.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>4210288560.2</v>
+        <v>4389026707.8</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>2893256394.5</t>
+          <t>2892223299.6</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>2808126948.8</v>
+        <v>2780910122.44</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>1317032165</t>
+          <t>1496803408</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>67944137.9742843</t>
+          <t>127502634.1471599</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>657522973.3642759</t>
+          <t>455074363.0979757</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>6678368784.0</t>
+          <t>2229434678.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>110.14</t>
+          <t>106.39</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>175702</t>
+          <t>169720</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>201756.824</t>
+          <t>201436.815</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>15.64</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>45.52</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>56.96</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-7.43</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>1,077</t>
+          <t>990</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>264591</t>
+          <t>195863</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.25</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>79.17</t>
+          <t>87.64</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>7.21</v>
+        <v>1.96</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.68</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>30.45</v>
+        <v>30.59</v>
       </c>
       <c r="BA27" t="n">
-        <v>30.21</v>
+        <v>30.26</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>87.50</t>
+          <t>76.40</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-84.39</t>
+          <t>-80.70</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,48 +13397,48 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>1480089801.70082</t>
+          <t>1500402533.868098</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>6703778205.0</t>
+          <t>6678368784.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>3070110512.8</v>
+        <v>4210288560.2</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>2633033521.2</t>
+          <t>2893256394.5</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>2766125687.26</v>
+        <v>2808126948.8</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>437076991</t>
+          <t>1317032165</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-39252013.91480508</t>
+          <t>67944137.9742843</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>446580799.0531235</t>
+          <t>657522973.3642759</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>6703778205.0</t>
+          <t>6678368784.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>110.14</t>
+          <t>106.39</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>175702</t>
+          <t>169720</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>173832.442</t>
+          <t>201756.824</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,177 +13625,177 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>33.45</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>12.66</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>16.60</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2025-12-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
           <t>31.65</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>20.18</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>-9.73</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>31.65</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>5.69</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
         <is>
           <t>2025-12-24 00:00:00</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>2025-12-24 00:00:00</t>
-        </is>
-      </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>57.05</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,67 +13806,67 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>1,077</t>
+          <t>990</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>264591</t>
+          <t>195863</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>59.72</t>
+          <t>79.17</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>4.08</v>
+        <v>7.21</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.45</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>7.40</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>30.24</v>
+        <v>30.45</v>
       </c>
       <c r="BA28" t="n">
-        <v>30.08</v>
+        <v>30.21</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>28.01</t>
+          <t>28.14</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>87.50</t>
         </is>
       </c>
       <c r="BD28" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BE28" t="n">
         <v>0.25</v>
       </c>
-      <c r="BE28" t="n">
-        <v>0.2</v>
-      </c>
       <c r="BF28" t="inlineStr">
         <is>
           <t>1.62</t>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-87.80</t>
+          <t>-84.39</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,48 +13884,48 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>1480089801.70082</t>
+          <t>1500402533.868098</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>5573788437.0</t>
+          <t>6703778205.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>1865132854</v>
+        <v>3070110512.8</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>2066069442.4</t>
+          <t>2633033521.2</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>2676628654.12</v>
+        <v>2766125687.26</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>-200936588</t>
+          <t>437076991</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-127585252.6362467</t>
+          <t>-39252013.91480508</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>126563083.5352938</t>
+          <t>446580799.0531235</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>5573788437.0</t>
+          <t>6703778205.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>110.14</t>
+          <t>106.39</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>175702</t>
+          <t>169720</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>32.45</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼胚.xlsx
+++ b/Result/checksun_type/不鏽鋼胚.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2925.0</t>
+          <t>3436.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>31.16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-32.04</t>
+          <t>-31.83</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,66 +1144,66 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>91.43</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>63.81</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.37</v>
+        <v>0.79</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>33.04</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>31.94</v>
+        <v>32.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>32.07</v>
+        <v>32.05</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>33.29</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>342.34</t>
+          <t>188.91</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-96.26</t>
+          <t>-92.92</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>304680.8126272912</t>
+          <t>304404.3902439025</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>96450.0</t>
+          <t>112454.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>92412.39999999999</v>
+        <v>102350.2</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>82555.7</t>
+          <t>78034.6</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>74595.14</v>
+        <v>75066.06</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>24315</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>2743.333087758422</t>
+          <t>3190.406522347275</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>3812.663379268575</t>
+          <t>5649.310412585968</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>96450.0</t>
+          <t>112454.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-11.23</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1588.0</t>
+          <t>2925.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-33.27</t>
+          <t>-32.04</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,66 +1631,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>68.57</t>
+          <t>63.81</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.46</v>
+        <v>1.37</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>31.84</v>
+        <v>31.94</v>
       </c>
       <c r="BA3" t="n">
         <v>32.07</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>2126.04</t>
+          <t>342.34</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-99.46</t>
+          <t>-96.26</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>304680.8126272912</t>
+          <t>304404.3902439025</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>51500.0</t>
+          <t>96450.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>83585.60000000001</v>
+        <v>92412.39999999999</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>79242.2</t>
+          <t>82555.7</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>73807.78</v>
+        <v>74595.14</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>2548.90939839294</t>
+          <t>2743.333087758422</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>2767.429639555587</t>
+          <t>3812.663379268575</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>51500.0</t>
+          <t>96450.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-11.23</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2495.0</t>
+          <t>1588.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-33.16</t>
+          <t>-33.27</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>7.82</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>68.57</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1.05</v>
+        <v>0.46</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>32.31</t>
+          <t>32.45</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>31.76</v>
+        <v>31.84</v>
       </c>
       <c r="BA4" t="n">
-        <v>32.08</v>
+        <v>32.07</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>543.24</t>
+          <t>2126.04</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-102.32</t>
+          <t>-99.46</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>304680.8126272912</t>
+          <t>304404.3902439025</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>82324.0</t>
+          <t>51500.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>82989.8</v>
+        <v>83585.60000000001</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>81392.6</t>
+          <t>79242.2</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>75011.82000000001</v>
+        <v>73807.78</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>2509.178445454278</t>
+          <t>2548.90939839294</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>5991.473238552891</t>
+          <t>2767.429639555587</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>82324.0</t>
+          <t>51500.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5123.0</t>
+          <t>2495.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-31.53</t>
+          <t>-33.16</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>54.29</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>3.88</v>
+        <v>1.05</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.31</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>31.67</v>
+        <v>31.76</v>
       </c>
       <c r="BA5" t="n">
-        <v>32.1</v>
+        <v>32.08</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>33.46</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>239.41</t>
+          <t>543.24</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-105.48</t>
+          <t>-102.32</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>304680.8126272912</t>
+          <t>304404.3902439025</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>169023.0</t>
+          <t>82324.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>74997.39999999999</v>
+        <v>82989.8</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>78680.3</t>
+          <t>81392.6</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>75523.48</v>
+        <v>75011.82000000001</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-3682</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>1876.033937618166</t>
+          <t>2509.178445454278</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>7080.697192886437</t>
+          <t>5991.473238552891</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>169023.0</t>
+          <t>82324.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>5123.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-21.19</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-34.80</t>
+          <t>-31.53</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,66 +3092,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.25</v>
+        <v>3.88</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.2</v>
+        <v>1.68</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>31.93</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>31.55</v>
+        <v>31.67</v>
       </c>
       <c r="BA6" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>33.46</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>82.03</t>
+          <t>239.41</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.02</v>
+        <v>0.11</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-108.76</t>
+          <t>-105.48</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>304680.8126272912</t>
+          <t>304404.3902439025</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>62765.0</t>
+          <t>169023.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>53719</v>
+        <v>74997.39999999999</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>68161.9</t>
+          <t>78680.3</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>74650.12</v>
+        <v>75523.48</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-14442</t>
+          <t>-3682</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>929.7315275693895</t>
+          <t>1876.033937618166</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-905.3292006687407</t>
+          <t>7080.697192886437</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>62765.0</t>
+          <t>169023.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-14.84</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1650.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-21.19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-35.11</t>
+          <t>-34.80</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>24.36</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-1.03</v>
+        <v>-0.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.61</v>
+        <v>1.2</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>31.93</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>31.52</v>
+        <v>31.55</v>
       </c>
       <c r="BA7" t="n">
-        <v>32.19</v>
+        <v>32.12</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>33.57</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>82.02</t>
+          <t>82.03</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-110.56</t>
+          <t>-108.76</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>304680.8126272912</t>
+          <t>304404.3902439025</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>52316.0</t>
+          <t>62765.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>72699</v>
+        <v>53719</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>71009.8</t>
+          <t>68161.9</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>75019.39999999999</v>
+        <v>74650.12</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>-14442</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>1263.378932703595</t>
+          <t>929.7315275693895</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-896.8194342951028</t>
+          <t>-905.3292006687407</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>52316.0</t>
+          <t>62765.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-15.24</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1515.0</t>
+          <t>1650.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-34.70</t>
+          <t>-35.11</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>74.32</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.09</v>
+        <v>1.61</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>31.5</v>
+        <v>31.52</v>
       </c>
       <c r="BA8" t="n">
-        <v>32.28</v>
+        <v>32.19</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>33.57</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>90.46</t>
+          <t>82.02</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.18</v>
+        <v>-0.15</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-112.72</t>
+          <t>-110.56</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>304680.8126272912</t>
+          <t>304404.3902439025</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>48521.0</t>
+          <t>52316.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>74898.8</v>
+        <v>72699</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>76512.7</t>
+          <t>71009.8</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>75902.94</v>
+        <v>75019.39999999999</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-1613</t>
+          <t>1689</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>1656.142272157904</t>
+          <t>1263.378932703595</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>266.9023546063399</t>
+          <t>-896.8194342951028</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>48521.0</t>
+          <t>52316.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-15.24</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1325.0</t>
+          <t>1515.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-34.29</t>
+          <t>-34.70</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,66 +4553,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>90.99</t>
+          <t>74.32</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.22</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>32.16</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>31.48</v>
+        <v>31.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>32.36</v>
+        <v>32.28</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.46</t>
         </is>
       </c>
       <c r="BD9" t="n">
         <v>-0.02</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.22</v>
+        <v>-0.18</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-115.60</t>
+          <t>-112.72</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>304680.8126272912</t>
+          <t>304404.3902439025</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>42362.0</t>
+          <t>48521.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>79795.39999999999</v>
+        <v>74898.8</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>75614.5</t>
+          <t>76512.7</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>75871.44</v>
+        <v>75902.94</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>-1613</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>1908.73134807637</t>
+          <t>1656.142272157904</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>2326.43696894389</t>
+          <t>266.9023546063399</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>42362.0</t>
+          <t>48521.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-14.17</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1966.0</t>
+          <t>1325.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,12 +5040,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5055,51 +5055,51 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>90.99</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.03</v>
+        <v>-0.22</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>32.17</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>31.45</v>
+        <v>31.48</v>
       </c>
       <c r="BA10" t="n">
-        <v>32.44</v>
+        <v>32.36</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>33.79</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>79.88</t>
+          <t>88.78</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.27</v>
+        <v>-0.22</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-119.06</t>
+          <t>-115.60</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>304680.8126272912</t>
+          <t>304404.3902439025</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>62631.0</t>
+          <t>42362.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>82363.2</v>
+        <v>79795.39999999999</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>77673.9</t>
+          <t>75614.5</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>75816.44</v>
+        <v>75871.44</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>1832.784871555003</t>
+          <t>1908.73134807637</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>5845.435097678099</t>
+          <t>2326.43696894389</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>62631.0</t>
+          <t>42362.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,17 +5284,17 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4838.0</t>
+          <t>1966.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-33.78</t>
+          <t>-34.29</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>23.83</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>31.44</v>
+        <v>31.45</v>
       </c>
       <c r="BA11" t="n">
-        <v>32.52</v>
+        <v>32.44</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>33.79</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>71.83</t>
+          <t>79.88</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.33</v>
+        <v>-0.27</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-122.87</t>
+          <t>-119.06</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>304680.8126272912</t>
+          <t>304404.3902439025</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>157665.0</t>
+          <t>62631.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>82604.8</v>
+        <v>82363.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>76417.1</t>
+          <t>77673.9</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>75403.94</v>
+        <v>75816.44</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>1103.212103168985</t>
+          <t>1832.784871555003</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>8492.13117095278</t>
+          <t>5845.435097678099</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>157665.0</t>
+          <t>62631.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-14.17</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-21.32</t>
+          <t>-31.30</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>24.30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6029,18 +6029,18 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-0.76</v>
+        <v>-0.17</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.92</v>
+        <v>0.27</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -6050,30 +6050,30 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>28.56</v>
+        <v>28.57</v>
       </c>
       <c r="BA12" t="n">
-        <v>28.39</v>
+        <v>28.4</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-18.05</t>
+          <t>-27.08</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-40.39</t>
+          <t>-44.17</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6097,38 +6097,38 @@
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>292.6</v>
+        <v>256.5</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>371.9</t>
+          <t>373.35</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>280.26</v>
+        <v>282.09</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-79</t>
+          <t>-116</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>9.722151767920694</t>
+          <t>8.361922419523479</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>8.425285598112964</t>
+          <t>0.8806610033387869</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>256.5</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,149 +6320,149 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>28.6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-21.32</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>28.05</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-54.58</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2026-01-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>32.65</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>32.4</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>-9.88</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>2026/01/09</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
         <is>
           <t>28.05</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>32.4</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>-3.94</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>-9.88</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>2026/01/09</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
       <c r="AI13" t="inlineStr">
         <is>
           <t>2025/12/16</t>
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>24.30</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6506,45 +6506,45 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-2.84</v>
+        <v>-0.76</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.15</v>
+        <v>0.92</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>28.87</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>28.54</v>
+        <v>28.56</v>
       </c>
       <c r="BA13" t="n">
-        <v>28.38</v>
+        <v>28.39</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
@@ -6553,15 +6553,15 @@
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-18.05</t>
         </is>
       </c>
       <c r="BD13" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BE13" t="n">
         <v>0.19</v>
       </c>
-      <c r="BE13" t="n">
-        <v>0.2</v>
-      </c>
       <c r="BF13" t="inlineStr">
         <is>
           <t>0.32</t>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-37.70</t>
+          <t>-40.39</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6584,43 +6584,43 @@
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>150.4</v>
+        <v>292.6</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>331.1</t>
+          <t>371.9</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>268.36</v>
+        <v>280.26</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-180</t>
+          <t>-79</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>9.957945616976644</t>
+          <t>9.722151767920694</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-32.90115375214216</t>
+          <t>8.425285598112964</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,17 +6680,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6782,7 +6782,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-40.21</t>
+          <t>-54.58</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6993,58 +6993,58 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-1.91</v>
+        <v>-2.84</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.82</v>
+        <v>1.15</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>28.87</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>28.56</v>
+        <v>28.54</v>
       </c>
       <c r="BA14" t="n">
         <v>28.38</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="BE14" t="n">
         <v>0.2</v>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-36.76</t>
+          <t>-37.70</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7071,38 +7071,38 @@
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>212</v>
+        <v>150.4</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>354.6</t>
+          <t>331.1</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>274.62</v>
+        <v>268.36</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-142</t>
+          <t>-180</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>17.75050913863461</t>
+          <t>9.957945616976644</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-14.47816876135875</t>
+          <t>-32.90115375214216</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,17 +7167,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,149 +7294,149 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-40.21</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>29.2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-2.1</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>48.81</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2026-01-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>28.05</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>29.2</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>32.65</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>32.4</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>-1.37</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>-9.88</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>2026/01/09</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>28.05</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>32.4</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>-9.88</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>2026/01/09</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
       <c r="AI15" t="inlineStr">
         <is>
           <t>2025/12/16</t>
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7480,42 +7480,42 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-1.68</v>
+        <v>-1.91</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.1</v>
+        <v>2.82</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.36</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>28.53</v>
+        <v>28.56</v>
       </c>
       <c r="BA15" t="n">
         <v>28.38</v>
@@ -7527,14 +7527,14 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>73.81</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-42.82</t>
+          <t>-36.76</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7558,38 +7558,38 @@
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>519.2</v>
+        <v>212</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>348.9</t>
+          <t>354.6</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>275.21</v>
+        <v>274.62</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>-142</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>23.61026875681522</t>
+          <t>17.75050913863461</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>6.250315824094628</t>
+          <t>-14.47816876135875</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7659,12 +7659,12 @@
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,22 +7791,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>48.81</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7967,61 +7967,61 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>52.27</t>
+          <t>40.91</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-0.24</v>
+        <v>-1.68</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.67</v>
+        <v>4.1</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>28.48</v>
+        <v>28.53</v>
       </c>
       <c r="BA16" t="n">
-        <v>28.37</v>
+        <v>28.38</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>115.36</t>
+          <t>73.81</t>
         </is>
       </c>
       <c r="BD16" t="n">
         <v>0.32</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-53.37</t>
+          <t>-42.82</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8045,43 +8045,43 @@
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>437.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>490.2</v>
+        <v>519.2</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>377.2</t>
+          <t>348.9</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>272.92</v>
+        <v>275.21</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>170</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>26.7666238354917</t>
+          <t>23.61026875681522</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>26.21063966673887</t>
+          <t>6.250315824094628</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>437.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>29.96</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,22 +8428,22 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>14.02</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr"/>
@@ -8454,61 +8454,61 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>52.27</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-1.5</v>
+        <v>-0.24</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.09</v>
+        <v>3.67</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>28.41</v>
+        <v>28.48</v>
       </c>
       <c r="BA17" t="n">
-        <v>28.35</v>
+        <v>28.37</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>178.33</t>
+          <t>115.36</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-66.82</t>
+          <t>-53.37</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8532,38 +8532,38 @@
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>437.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>451.2</v>
+        <v>490.2</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>384.7</t>
+          <t>377.2</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>265.32</v>
+        <v>272.92</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>113</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>26.86771186617403</t>
+          <t>26.7666238354917</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>25.50357945384718</t>
+          <t>26.21063966673887</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>437.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,17 +8628,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,12 +8915,12 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -8941,45 +8941,45 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>4.52</v>
+        <v>-1.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.82</v>
+        <v>3.09</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>28.38</v>
+        <v>28.41</v>
       </c>
       <c r="BA18" t="n">
-        <v>28.36</v>
+        <v>28.35</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
@@ -8988,14 +8988,14 @@
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>442.46</t>
+          <t>178.33</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-81.61</t>
+          <t>-66.82</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9019,38 +9019,38 @@
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>336.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>511.8</v>
+        <v>451.2</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>387.4</t>
+          <t>384.7</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>273</v>
+        <v>265.32</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>66</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>27.11573594114255</t>
+          <t>26.86771186617403</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>67.29693702636456</t>
+          <t>25.50357945384718</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>336.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,17 +9115,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9217,7 +9217,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,22 +9402,22 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>51.40</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr"/>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9442,47 +9442,47 @@
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>6.12</v>
+        <v>4.52</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.66</v>
+        <v>2.82</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>29.18</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>28.27</v>
+        <v>28.38</v>
       </c>
       <c r="BA19" t="n">
-        <v>28.33</v>
+        <v>28.36</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>2937.20</t>
+          <t>442.46</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-101.95</t>
+          <t>-81.61</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9506,38 +9506,38 @@
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>1621.0</t>
+          <t>336.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>497.2</v>
+        <v>511.8</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>412.9</t>
+          <t>387.4</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>266.86</v>
+        <v>273</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>124</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>19.81006301655673</t>
+          <t>27.11573594114255</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>91.7054143790192</t>
+          <t>67.29693702636456</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>1621.0</t>
+          <t>336.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,149 +9729,149 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-6.64</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>20.42</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>28.05</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>32.65</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>32.4</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>8.73</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>-9.88</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
           <t>28.3</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-36.76</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2026-01-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>2026/01/09</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
         <is>
           <t>28.05</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>32.4</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>-9.88</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>2026/01/09</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
       <c r="AI20" t="inlineStr">
         <is>
           <t>2025/12/16</t>
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.40</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -9929,48 +9929,48 @@
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.51</v>
+        <v>1.66</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
           <t>-0.46</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>28.74</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>28.16</v>
+        <v>28.27</v>
       </c>
       <c r="BA20" t="n">
-        <v>28.29</v>
+        <v>28.33</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>2937.20</t>
         </is>
       </c>
       <c r="BD20" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BE20" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BE20" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="BF20" t="inlineStr">
         <is>
           <t>0.32</t>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-116.28</t>
+          <t>-101.95</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9993,38 +9993,38 @@
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1621.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>178.6</v>
+        <v>497.2</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>282.425</t>
+          <t>412.9</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>243.94</v>
+        <v>266.86</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-103</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>6.738180950654459</t>
+          <t>19.81006301655673</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-14.37909705929633</t>
+          <t>91.7054143790192</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>1621.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10231,12 +10231,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-19.97</t>
+          <t>-36.76</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10419,16 +10419,16 @@
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
           <t>-0.53</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>-0.47</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -10440,23 +10440,23 @@
         <v>28.16</v>
       </c>
       <c r="BA21" t="n">
-        <v>28.31</v>
+        <v>28.29</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>72.12</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-119.84</t>
+          <t>-116.28</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10484,34 +10484,34 @@
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>264.2</v>
+        <v>178.6</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>330.125</t>
+          <t>282.425</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>252.14</v>
+        <v>243.94</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-65</t>
+          <t>-103</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>10.57768604337278</t>
+          <t>6.738180950654459</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>5.263711495227881</t>
+          <t>-14.37909705929633</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>241477.642</t>
+          <t>277315.402</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10718,12 +10718,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>36.66</t>
+          <t>37.80</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>24.96</t>
+          <t>31.12</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>78.41</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,275</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>241478</t>
+          <t>277315</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>98.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>85.23</t>
+          <t>90.93</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>3.45</v>
+        <v>5.54</v>
       </c>
       <c r="AV22" t="n">
-        <v>15.66</v>
+        <v>17.24</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>38.23</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>33.05</v>
+        <v>33.54</v>
       </c>
       <c r="BA22" t="n">
-        <v>31.26</v>
+        <v>31.49</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>56.15</t>
+          <t>54.47</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,24 +10962,24 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>1540897976.553972</t>
+          <t>1571693141.496951</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>9582741257.0</t>
+          <t>11128079419.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>8164652251.4</v>
+        <v>8846108515.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>5974633594.9</t>
+          <t>6419604658.4</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>3263958224.1</v>
+        <v>3452687768.5</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
@@ -10988,22 +10988,22 @@
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>603685023.0471929</t>
+          <t>701231041.868694</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>1029518558.995068</t>
+          <t>1237734145.38695</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>9582741257.0</t>
+          <t>11128079419.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11043,42 +11043,42 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="CA22" t="inlineStr">
+        <is>
+          <t>-6.059105961166755</t>
+        </is>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>-29.72089430657912</t>
+        </is>
+      </c>
+      <c r="CC22" t="inlineStr">
+        <is>
+          <t>-4.098016323960095</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>1.18</t>
         </is>
       </c>
-      <c r="CA22" t="inlineStr">
-        <is>
-          <t>-6.059105961166755</t>
-        </is>
-      </c>
-      <c r="CB22" t="inlineStr">
-        <is>
-          <t>-29.72089430657912</t>
-        </is>
-      </c>
-      <c r="CC22" t="inlineStr">
-        <is>
-          <t>-4.098016323960095</t>
-        </is>
-      </c>
-      <c r="CD22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>價跌量-</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>109.86</t>
+          <t>115.28</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>175259</t>
+          <t>183900</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>153666.727</t>
+          <t>241477.642</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>28.16</t>
+          <t>36.66</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>24.96</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,275</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>241478</t>
+          <t>277315</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>74.05</t>
+          <t>98.73</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>85.65</t>
+          <t>85.23</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>1.51</v>
+        <v>3.45</v>
       </c>
       <c r="AV23" t="n">
-        <v>13.79</v>
+        <v>15.66</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>32.55</v>
+        <v>33.05</v>
       </c>
       <c r="BA23" t="n">
-        <v>31.08</v>
+        <v>31.26</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>62.01</t>
+          <t>56.15</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-26.71</t>
+          <t>-14.74</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,48 +11449,48 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>1540897976.553972</t>
+          <t>1571693141.496951</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>5673303694.0</t>
+          <t>9582741257.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>7287931238.8</v>
+        <v>8164652251.4</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>5686737289.7</t>
+          <t>5974633594.9</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>3133201605.06</v>
+        <v>3263958224.1</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>1601193949</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>526260743.7839429</t>
+          <t>603685023.0471929</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>860871147.2568426</t>
+          <t>1029518558.995068</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>5673303694.0</t>
+          <t>9582741257.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>109.86</t>
+          <t>115.28</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>175259</t>
+          <t>183900</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
+          <t>40.45</t>
+        </is>
+      </c>
+      <c r="CS23" t="inlineStr">
+        <is>
           <t>38.5</t>
         </is>
       </c>
-      <c r="CS23" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>39.55</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>195862.867</t>
+          <t>153666.727</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>28.16</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>21.01</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>55.38</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,66 +11858,66 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,275</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>241478</t>
+          <t>277315</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>82.91</t>
+          <t>74.05</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>85.65</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>6.09</v>
+        <v>1.51</v>
       </c>
       <c r="AV24" t="n">
-        <v>12.23</v>
+        <v>13.79</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>32.17</v>
+        <v>32.55</v>
       </c>
       <c r="BA24" t="n">
-        <v>30.93</v>
+        <v>31.08</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>79.03</t>
+          <t>62.01</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-38.07</t>
+          <t>-26.71</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,48 +11936,48 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>1540897976.553972</t>
+          <t>1571693141.496951</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>7608677221.0</t>
+          <t>5673303694.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>6630219145.4</v>
+        <v>7287931238.8</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>5676785764.0</t>
+          <t>5686737289.7</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>3052834273.88</v>
+        <v>3133201605.06</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>953433381</t>
+          <t>1601193949</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>465422488.6070521</t>
+          <t>526260743.7839429</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>1008069185.550203</t>
+          <t>860871147.2568426</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>7608677221.0</t>
+          <t>5673303694.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12037,22 +12037,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>109.86</t>
+          <t>115.28</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>175259</t>
+          <t>183900</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>264591.244</t>
+          <t>195862.867</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>21.01</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>74.82</t>
+          <t>55.38</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,66 +12345,66 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,275</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>241478</t>
+          <t>277315</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.91</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>13.94</v>
+        <v>6.09</v>
       </c>
       <c r="AV25" t="n">
-        <v>9.48</v>
+        <v>12.23</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>31.79</v>
+        <v>32.17</v>
       </c>
       <c r="BA25" t="n">
-        <v>30.79</v>
+        <v>30.93</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>29.34</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>79.03</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-50.31</t>
+          <t>-38.07</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,48 +12423,48 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>1540897976.553972</t>
+          <t>1571693141.496951</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>10237740986.0</t>
+          <t>7608677221.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>5594762063</v>
+        <v>6630219145.4</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>4991894385.4</t>
+          <t>5676785764.0</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>2978303860.6</v>
+        <v>3052834273.88</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>602867677</t>
+          <t>953433381</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>366759452.7992064</t>
+          <t>465422488.6070521</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>974988177.1639261</t>
+          <t>1008069185.550203</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>10237740986.0</t>
+          <t>7608677221.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>30.21</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12524,22 +12524,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>109.86</t>
+          <t>115.28</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>175259</t>
+          <t>183900</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>217071.602</t>
+          <t>264591.244</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>25.28</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>61.38</t>
+          <t>74.82</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,275</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>241478</t>
+          <t>277315</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12847,51 +12847,51 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>94.84</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>8.52</v>
+        <v>13.94</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.92</v>
+        <v>9.48</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>33.22000000000001</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>31.36</v>
+        <v>31.79</v>
       </c>
       <c r="BA26" t="n">
-        <v>30.6</v>
+        <v>30.79</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>67.96</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>1.05</v>
+        <v>1.54</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.62</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-61.59</t>
+          <t>-50.31</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,48 +12910,48 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>1540897976.553972</t>
+          <t>1571693141.496951</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>7720798099.0</t>
+          <t>10237740986.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>3993100801.4</v>
+        <v>5594762063</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>4101694680.8</t>
+          <t>4991894385.4</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>2883137343.96</v>
+        <v>2978303860.6</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-108593879</t>
+          <t>602867677</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>256172412.005621</t>
+          <t>366759452.7992064</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>611223184.0348191</t>
+          <t>974988177.1639261</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>7720798099.0</t>
+          <t>10237740986.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="BS26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>30.21</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>109.86</t>
+          <t>115.28</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>175259</t>
+          <t>183900</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>152715.387</t>
+          <t>217071.602</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>15.04</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>43.18</t>
+          <t>61.38</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,275</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>241478</t>
+          <t>277315</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13334,51 +13334,51 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>80.91</t>
+          <t>94.84</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>3.48</v>
+        <v>8.52</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.48</v>
+        <v>5.92</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>33.22000000000001</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>31.08</v>
+        <v>31.36</v>
       </c>
       <c r="BA27" t="n">
-        <v>30.47</v>
+        <v>30.6</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>48.81</t>
+          <t>67.96</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>0.77</v>
+        <v>1.05</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-68.12</t>
+          <t>-61.59</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,48 +13397,48 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>1540897976.553972</t>
+          <t>1571693141.496951</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>5199136194.0</t>
+          <t>7720798099.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>3784614938.4</v>
+        <v>3993100801.4</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>3427362725.6</t>
+          <t>4101694680.8</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>2765585656.86</v>
+        <v>2883137343.96</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>357252212</t>
+          <t>-108593879</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>191617726.1821304</t>
+          <t>256172412.005621</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>339401960.8848505</t>
+          <t>611223184.0348191</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>5199136194.0</t>
+          <t>7720798099.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>109.86</t>
+          <t>115.28</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>175259</t>
+          <t>183900</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>73283.072</t>
+          <t>152715.387</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>37.31</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>43.18</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,66 +13806,66 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,275</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>241478</t>
+          <t>277315</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>84.51</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>66.57</t>
+          <t>80.91</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>1.42</v>
+        <v>3.48</v>
       </c>
       <c r="AV28" t="n">
-        <v>4.88</v>
+        <v>4.48</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>30.93</v>
+        <v>31.08</v>
       </c>
       <c r="BA28" t="n">
-        <v>30.4</v>
+        <v>30.47</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>44.06</t>
+          <t>48.81</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>0.65</v>
+        <v>0.77</v>
       </c>
       <c r="BE28" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-72.01</t>
+          <t>-68.12</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,48 +13884,48 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>1540897976.553972</t>
+          <t>1571693141.496951</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>2384743227.0</t>
+          <t>5199136194.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>4085543340.6</v>
+        <v>3784614938.4</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>2975338097.3</t>
+          <t>3427362725.6</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>2713094571.68</v>
+        <v>2765585656.86</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>1110205243</t>
+          <t>357252212</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>164747865.3270903</t>
+          <t>191617726.1821304</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>209142490.4604368</t>
+          <t>339401960.8848505</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>2384743227.0</t>
+          <t>5199136194.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -13985,22 +13985,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>109.86</t>
+          <t>115.28</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>175259</t>
+          <t>183900</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>75139.115</t>
+          <t>73283.072</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>62.84</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -14142,7 +14142,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -14192,7 +14192,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -14222,7 +14222,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -14272,17 +14272,17 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -14293,66 +14293,66 @@
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,275</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>241478</t>
+          <t>277315</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>58.23</t>
+          <t>84.51</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>62.15</t>
+          <t>66.57</t>
         </is>
       </c>
       <c r="AU29" t="n">
-        <v>-1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.5</v>
+        <v>4.88</v>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>30.8</v>
+        <v>30.93</v>
       </c>
       <c r="BA29" t="n">
-        <v>30.34</v>
+        <v>30.4</v>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>28.62</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>40.69</t>
+          <t>44.06</t>
         </is>
       </c>
       <c r="BD29" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="BE29" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>-75.09</t>
+          <t>-72.01</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
@@ -14371,48 +14371,48 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>1540897976.553972</t>
+          <t>1571693141.496951</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
         <is>
-          <t>2431391809.0</t>
+          <t>2384743227.0</t>
         </is>
       </c>
       <c r="BK29" t="n">
-        <v>4723352382.6</v>
+        <v>4085543340.6</v>
       </c>
       <c r="BL29" t="inlineStr">
         <is>
-          <t>2900573138.0</t>
+          <t>2975338097.3</t>
         </is>
       </c>
       <c r="BM29" t="n">
-        <v>2734281368.9</v>
+        <v>2713094571.68</v>
       </c>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>1822779244</t>
+          <t>1110205243</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>156676115.3028455</t>
+          <t>164747865.3270903</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>317130261.6591163</t>
+          <t>209142490.4604368</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>2431391809.0</t>
+          <t>2384743227.0</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="BU29" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="BV29" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -14472,22 +14472,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="CI29" t="inlineStr">
         <is>
-          <t>109.86</t>
+          <t>115.28</t>
         </is>
       </c>
       <c r="CJ29" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
         <is>
-          <t>175259</t>
+          <t>183900</t>
         </is>
       </c>
       <c r="CN29" t="inlineStr">
@@ -14537,22 +14537,22 @@
       </c>
       <c r="CQ29" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CR29" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CT29" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="CU29" t="inlineStr">
@@ -14584,12 +14584,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>70250.984</t>
+          <t>75139.115</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -14609,17 +14609,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>23.37</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>51.75</t>
+          <t>62.84</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -14759,17 +14759,17 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -14780,66 +14780,66 @@
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,275</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>241478</t>
+          <t>277315</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>56.96</t>
+          <t>58.23</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>76.07</t>
+          <t>62.15</t>
         </is>
       </c>
       <c r="AU30" t="n">
-        <v>-0.59</v>
+        <v>-1.21</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>30.71</v>
+        <v>30.8</v>
       </c>
       <c r="BA30" t="n">
-        <v>30.31</v>
+        <v>30.34</v>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.51</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>40.69</t>
         </is>
       </c>
       <c r="BD30" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="BE30" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>-77.63</t>
+          <t>-75.09</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -14858,48 +14858,48 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>1540897976.553972</t>
+          <t>1571693141.496951</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
-          <t>2229434678.0</t>
+          <t>2431391809.0</t>
         </is>
       </c>
       <c r="BK30" t="n">
-        <v>4389026707.8</v>
+        <v>4723352382.6</v>
       </c>
       <c r="BL30" t="inlineStr">
         <is>
-          <t>2892223299.6</t>
+          <t>2900573138.0</t>
         </is>
       </c>
       <c r="BM30" t="n">
-        <v>2780910122.44</v>
+        <v>2734281368.9</v>
       </c>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>1496803408</t>
+          <t>1822779244</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>127502634.1471599</t>
+          <t>156676115.3028455</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>455074363.0979757</t>
+          <t>317130261.6591163</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>2229434678.0</t>
+          <t>2431391809.0</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="BU30" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BV30" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="CI30" t="inlineStr">
         <is>
-          <t>109.86</t>
+          <t>115.28</t>
         </is>
       </c>
       <c r="CJ30" t="inlineStr">
@@ -14999,12 +14999,12 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
         <is>
-          <t>175259</t>
+          <t>183900</t>
         </is>
       </c>
       <c r="CN30" t="inlineStr">
@@ -15024,22 +15024,22 @@
       </c>
       <c r="CQ30" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CR30" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CT30" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CU30" t="inlineStr">
@@ -15071,12 +15071,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>201436.815</t>
+          <t>70250.984</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -15096,17 +15096,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>18.33</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>51.75</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-01-13 00:00:00</t>
+          <t>2026-01-14 00:00:00</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -15246,87 +15246,87 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>56.96</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>-7.43</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>1,081</t>
+          <t>1,275</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>241478</t>
+          <t>277315</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>56.96</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>87.64</t>
+          <t>76.07</t>
         </is>
       </c>
       <c r="AU31" t="n">
-        <v>1.96</v>
+        <v>-0.59</v>
       </c>
       <c r="AV31" t="n">
-        <v>3.55</v>
+        <v>4.01</v>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>31.68</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>30.59</v>
+        <v>30.71</v>
       </c>
       <c r="BA31" t="n">
-        <v>30.26</v>
+        <v>30.31</v>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>76.40</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="BD31" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BE31" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>-80.70</t>
+          <t>-77.63</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
@@ -15345,48 +15345,48 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>1540897976.553972</t>
+          <t>1571693141.496951</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
         <is>
-          <t>6678368784.0</t>
+          <t>2229434678.0</t>
         </is>
       </c>
       <c r="BK31" t="n">
-        <v>4210288560.2</v>
+        <v>4389026707.8</v>
       </c>
       <c r="BL31" t="inlineStr">
         <is>
-          <t>2893256394.5</t>
+          <t>2892223299.6</t>
         </is>
       </c>
       <c r="BM31" t="n">
-        <v>2808126948.8</v>
+        <v>2780910122.44</v>
       </c>
       <c r="BN31" t="inlineStr">
         <is>
-          <t>1317032165</t>
+          <t>1496803408</t>
         </is>
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>67944137.9742843</t>
+          <t>127502634.1471599</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>657522973.3642759</t>
+          <t>455074363.0979757</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>6678368784.0</t>
+          <t>2229434678.0</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="BU31" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BV31" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -15456,12 +15456,12 @@
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -15471,7 +15471,7 @@
       </c>
       <c r="CI31" t="inlineStr">
         <is>
-          <t>109.86</t>
+          <t>115.28</t>
         </is>
       </c>
       <c r="CJ31" t="inlineStr">
@@ -15486,12 +15486,12 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
         <is>
-          <t>175259</t>
+          <t>183900</t>
         </is>
       </c>
       <c r="CN31" t="inlineStr">
@@ -15511,22 +15511,22 @@
       </c>
       <c r="CQ31" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CR31" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CT31" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="CU31" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼胚.xlsx
+++ b/Result/checksun_type/不鏽鋼胚.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX34"/>
+  <dimension ref="A1:CY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,6 +939,11 @@
           <t>盤整震盪_前15日次數</t>
         </is>
       </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>多頭排列_前5日次數</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -978,12 +983,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -998,119 +1003,119 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-01-29 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-02-02 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2025-02-24 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2025-02-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>37.4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2025/09/26</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>35.6</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2025/06/16</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
           <t>33.6</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>48.85</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-1.49</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>-28.05</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>37.4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>35.6</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2025/06/16</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2026/02/02</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>33.6</t>
-        </is>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>2026/01/28</t>
@@ -1123,7 +1128,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-07-02 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1149,12 +1154,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1212,12 +1217,12 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-68.30</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1227,7 +1232,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>300674.2721893491</t>
+          <t>182992.008</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1253,12 +1258,12 @@
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>8804.02927943702</t>
+          <t>8804.02927943345</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>8774.043462939328</t>
+          <t>8774.043462938556</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1343,7 +1348,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1353,7 +1358,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1368,12 +1373,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1428,7 +1433,12 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1480,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1485,124 +1495,124 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-01-29 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-02-02 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2025-02-24 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2025-02-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>37.4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/09/26</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>35.6</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/06/16</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
           <t>33.6</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>35.15</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>48.85</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>-4.41</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-28.05</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>37.4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>35.6</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/06/16</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2026/02/02</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>33.6</t>
-        </is>
-      </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>2026/01/28</t>
@@ -1615,7 +1625,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-07-02 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1641,12 +1651,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1704,12 +1714,12 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-67.03</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1719,7 +1729,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>300674.2721893491</t>
+          <t>182992.008</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1745,12 +1755,12 @@
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>8809.481246072963</t>
+          <t>8809.481246068885</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>15452.15910015668</t>
+          <t>15452.1591001558</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1760,7 +1770,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1835,7 +1845,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1845,7 +1855,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1860,12 +1870,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1920,7 +1930,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1977,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1977,124 +1992,124 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-01-29 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-02-02 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2025-02-24 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2025-02-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>37.4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/09/26</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>35.6</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/06/16</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
           <t>33.6</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>35.15</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>48.85</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>-2.99</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-28.05</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>37.4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>35.6</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/06/16</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2026/02/02</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>33.6</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>2026/01/28</t>
@@ -2107,7 +2122,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-07-02 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -2133,12 +2148,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2196,12 +2211,12 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-66.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2211,7 +2226,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>300674.2721893491</t>
+          <t>182992.008</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2237,12 +2252,12 @@
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>7601.721636239559</t>
+          <t>7601.721636234901</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>19513.6043283187</t>
+          <t>19513.6043283177</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2252,7 +2267,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2327,7 +2342,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2337,7 +2352,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2352,12 +2367,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2412,7 +2427,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2474,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2469,124 +2489,124 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-01-29 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-02-02 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2025-02-24 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2025-02-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>37.4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2025/09/26</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>35.6</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2025/06/16</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
           <t>33.6</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>35.15</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>48.85</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>4.61</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-28.05</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>37.4</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>35.6</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2025/06/16</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2026/02/02</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>33.6</t>
-        </is>
-      </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>2026/01/28</t>
@@ -2599,7 +2619,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-07-02 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2625,12 +2645,12 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2688,12 +2708,12 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-67.83</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2703,7 +2723,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>300674.2721893491</t>
+          <t>182992.008</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2729,12 +2749,12 @@
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>5435.924783134261</t>
+          <t>5435.924783128939</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>21397.39735682453</t>
+          <t>21397.39735682339</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2744,7 +2764,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2819,7 +2839,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2829,7 +2849,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2844,12 +2864,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2904,7 +2924,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2971,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2966,119 +2991,119 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-01-29 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-02-02 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2025-02-24 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2025-02-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>37.4</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2025/09/26</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>35.6</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2025/06/16</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
           <t>33.6</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>48.85</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-0.74</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-28.05</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>37.4</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>35.6</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2025/06/16</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>2026/02/02</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>33.6</t>
-        </is>
-      </c>
       <c r="AI6" t="inlineStr">
         <is>
           <t>2026/01/28</t>
@@ -3091,7 +3116,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-07-02 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -3117,12 +3142,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3180,12 +3205,12 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-69.09</t>
+          <t>-6.40</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3195,7 +3220,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>300674.2721893491</t>
+          <t>182992.008</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -3221,12 +3246,12 @@
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>2533.838860645122</t>
+          <t>2533.838860639038</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-1292.805365196589</t>
+          <t>-1292.805365197884</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3311,7 +3336,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3321,7 +3346,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3336,12 +3361,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3396,7 +3421,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -3438,12 +3468,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3458,119 +3488,119 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-01-29 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-02-02 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2025-02-24 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2025-02-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>37.4</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2025/09/26</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>35.6</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2025/06/16</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
           <t>33.6</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>48.85</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-0.89</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>-28.05</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>37.4</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>35.6</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025/06/16</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2026/02/02</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>33.6</t>
-        </is>
-      </c>
       <c r="AI7" t="inlineStr">
         <is>
           <t>2026/01/28</t>
@@ -3583,7 +3613,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-07-02 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3609,12 +3639,12 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3672,12 +3702,12 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-68.86</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3687,7 +3717,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>300674.2721893491</t>
+          <t>182992.008</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -3713,12 +3743,12 @@
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>3229.592356252705</t>
+          <t>3229.592356245751</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-858.5662050411775</t>
+          <t>-858.5662050426617</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3803,7 +3833,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3813,7 +3843,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3828,12 +3858,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3888,7 +3918,12 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -3930,12 +3965,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3950,119 +3985,119 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-01-29 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-02-02 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2025-02-24 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2025-02-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>37.4</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2025/09/26</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>35.6</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2025/06/16</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
           <t>33.6</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>48.85</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>-28.05</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>37.4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>35.6</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2025/06/16</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2026/02/02</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>33.6</t>
-        </is>
-      </c>
       <c r="AI8" t="inlineStr">
         <is>
           <t>2026/01/28</t>
@@ -4075,7 +4110,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-07-02 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -4101,12 +4136,12 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4137,7 +4172,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>33.97000000000001</t>
         </is>
       </c>
       <c r="AZ8" t="n">
@@ -4164,12 +4199,12 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-69.40</t>
+          <t>-7.35</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4179,7 +4214,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>300674.2721893491</t>
+          <t>182992.008</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -4205,12 +4240,12 @@
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>3972.893912851593</t>
+          <t>3972.893912843644</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-278.4900403534266</t>
+          <t>-278.4900403551292</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4295,7 +4330,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4305,7 +4340,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4320,12 +4355,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4380,7 +4415,12 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -4422,12 +4462,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4442,119 +4482,119 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-01-29 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-02-02 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2025-02-24 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2025-02-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>37.4</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2025/09/26</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>35.6</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2025/06/16</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
           <t>33.6</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>48.85</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>-28.05</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>37.4</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>35.6</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2025/06/16</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>2026/02/02</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>33.6</t>
-        </is>
-      </c>
       <c r="AI9" t="inlineStr">
         <is>
           <t>2026/01/28</t>
@@ -4567,7 +4607,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-07-02 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4593,12 +4633,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4633,7 +4673,7 @@
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>32.95</v>
+        <v>32.94</v>
       </c>
       <c r="BA9" t="n">
         <v>32.05</v>
@@ -4656,12 +4696,12 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-71.09</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4671,7 +4711,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>300674.2721893491</t>
+          <t>182992.008</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -4697,12 +4737,12 @@
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>4745.872813434324</t>
+          <t>4745.872813425239</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>2381.029124927416</t>
+          <t>2381.029124925466</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4777,7 +4817,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4787,7 +4827,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4797,7 +4837,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4812,12 +4852,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4872,7 +4912,12 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -4914,12 +4959,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4934,119 +4979,119 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-01-29 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-02-02 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2025-02-24 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2025-02-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>37.4</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2025/09/26</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>35.6</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2025/06/16</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
           <t>33.6</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>48.85</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>-28.05</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>37.4</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>35.6</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2025/06/16</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>2026/02/02</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>33.6</t>
-        </is>
-      </c>
       <c r="AI10" t="inlineStr">
         <is>
           <t>2026/01/28</t>
@@ -5059,7 +5104,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-07-02 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -5085,12 +5130,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5121,7 +5166,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>33.85000000000001</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="AZ10" t="n">
@@ -5148,12 +5193,12 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-72.93</t>
+          <t>-18.04</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5163,7 +5208,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>300674.2721893491</t>
+          <t>182992.008</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -5189,12 +5234,12 @@
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>5175.844393162852</t>
+          <t>5175.84439315247</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>5289.162606581202</t>
+          <t>5289.162606578975</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5269,7 +5314,7 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5279,7 +5324,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5289,7 +5334,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5304,12 +5349,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5364,7 +5409,12 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -5406,12 +5456,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -5426,119 +5476,119 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-01-29 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-02-02 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2025-02-24 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-02-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/08/27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>37.4</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2025/09/26</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>35.6</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2025/06/16</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
           <t>33.6</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>48.85</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>-28.05</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/08/27</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>37.4</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>35.6</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2025/06/16</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2026/02/02</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>33.6</t>
-        </is>
-      </c>
       <c r="AI11" t="inlineStr">
         <is>
           <t>2026/01/28</t>
@@ -5551,7 +5601,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-07-02 00:00:00</t>
+          <t>2025-09-01 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -5577,12 +5627,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5640,12 +5690,12 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-75.65</t>
+          <t>-26.27</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5655,7 +5705,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>300674.2721893491</t>
+          <t>182992.008</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -5681,12 +5731,12 @@
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>5155.241081632244</t>
+          <t>5155.241081620377</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>6000.811772994421</t>
+          <t>6000.811772991889</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5771,7 +5821,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5781,7 +5831,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5796,12 +5846,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5856,29 +5906,34 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY11" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>價_量;【b1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2652.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5888,7 +5943,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5898,17 +5953,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,37 +5973,37 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-01-29 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-02-02 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-02-24 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-02-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5958,12 +6013,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -5973,22 +6028,22 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>-28.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025/08/27</t>
+          <t>2025/11/07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5998,67 +6053,67 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2025/09/26</t>
+          <t>2025/11/11</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025/06/16</t>
+          <t>2025/11/03</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2026/02/02</t>
+          <t>2026/01/09</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2026/01/28</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-07-02 00:00:00</t>
+          <t>2026-02-04 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>13.06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6069,12 +6124,12 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6084,60 +6139,60 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>97.92</t>
+          <t>94.87</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>1.31</v>
+        <v>1.71</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>33.51000000000001</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>32.63</v>
+        <v>28.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>32.01</v>
+        <v>28.45</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>53.42</t>
+          <t>384.10</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.31</v>
+        <v>0.04</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-78.55</t>
+          <t>-82.09</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6147,43 +6202,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>300674.2721893491</t>
+          <t>623.0523012552302</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>90486.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>103999.2</v>
+        <v>659.25</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>103174.7</t>
+          <t>532.725</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>74418.24000000001</v>
+        <v>347.1</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>126</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>5001.50095593003</t>
+          <t>21.97897258649899</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>5396.353018834969</t>
+          <t>19.03763956639023</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>90486.0</t>
+          <t>659.25</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6193,27 +6248,27 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2026/01/14</t>
+          <t>2026/01/02</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>榮剛</t>
+          <t>唐榮公司</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>榮剛</t>
+          <t>唐榮公司</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
@@ -6228,134 +6283,139 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>3.374441834093832</t>
+          <t>29.8389724126963</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>-7.030655304464596</t>
+          <t>0.4355880318993286</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>-10.13626090778315</t>
+          <t>-21.22308305261796</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>19.09%</t>
+          <t>-11.19%</t>
         </is>
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>-14.27%</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>特殊鋼材料98.00%、其他2.00% (2024年)</t>
+          <t>不�袗�100.00% (2024年)</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>榮剛-鋼鐵工業-上櫃</t>
+          <t>唐榮公司-鋼鐵工業-上櫃</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
+          <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="CV12" t="inlineStr">
         <is>
-          <t>** 鋼鐵 - 鋼胚、不鏽鋼胚、不鏽鋼棒線</t>
+          <t>** 鋼鐵 - 不鏽鋼胚</t>
         </is>
       </c>
       <c r="CW12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="CY12" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6390,12 +6450,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -6405,137 +6465,137 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-02-03 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>2026/01/09</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>28.05</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>27.9</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
           <t>2026-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2024-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2024-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>-9.45</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>2026/01/09</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -6566,7 +6626,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6613,7 +6673,7 @@
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>7646.88</t>
+          <t>7646.90</t>
         </is>
       </c>
       <c r="BD13" t="n">
@@ -6624,12 +6684,12 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-99.50</t>
+          <t>-99.29</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6639,7 +6699,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>759.7741935483871</t>
+          <t>623.0523012552302</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -6665,12 +6725,12 @@
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>22.51376040832675</t>
+          <t>22.51376040833695</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>5.316111429502712</t>
+          <t>5.316111429504986</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -6680,7 +6740,7 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -6780,12 +6840,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6800,7 +6860,7 @@
       </c>
       <c r="CP13" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
+          <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
       <c r="CQ13" t="inlineStr">
@@ -6840,7 +6900,12 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="CY13" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6947,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -6902,132 +6967,132 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-02-03 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>2026/01/09</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>28.05</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>27.9</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
           <t>2026-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2024-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2024-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>-9.45</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>2026/01/09</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -7058,7 +7123,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -7116,12 +7181,12 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-109.11</t>
+          <t>-112.89</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7131,7 +7196,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>759.7741935483871</t>
+          <t>623.0523012552302</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -7157,12 +7222,12 @@
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>25.64060567720385</t>
+          <t>25.64060567721549</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>18.65799582575545</t>
+          <t>18.65799582575801</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -7272,12 +7337,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7292,7 +7357,7 @@
       </c>
       <c r="CP14" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
+          <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
       <c r="CQ14" t="inlineStr">
@@ -7332,7 +7397,12 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CY14" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7444,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -7394,132 +7464,132 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-02-03 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>2026/01/09</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>28.05</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>27.9</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
           <t>2026-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2024-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2024-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>-9.45</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>2026/01/09</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -7550,7 +7620,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -7608,12 +7678,12 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-113.88</t>
+          <t>-119.63</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7623,7 +7693,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>759.7741935483871</t>
+          <t>623.0523012552302</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -7649,12 +7719,12 @@
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>26.91017110473992</t>
+          <t>26.91017110475321</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>53.12290225519655</t>
+          <t>53.12290225519951</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -7764,12 +7834,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7784,7 +7854,7 @@
       </c>
       <c r="CP15" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
+          <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
       <c r="CQ15" t="inlineStr">
@@ -7824,7 +7894,12 @@
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CY15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7941,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7886,132 +7961,132 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-02-03 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>2026/01/09</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>28.05</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>27.9</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
           <t>2026-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2024-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2024-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>-9.45</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>2026/01/09</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -8042,7 +8117,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -8100,12 +8175,12 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-117.66</t>
+          <t>-124.99</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8115,7 +8190,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>759.7741935483871</t>
+          <t>623.0523012552302</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -8141,12 +8216,12 @@
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>22.14421998647508</t>
+          <t>22.14421998649025</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>62.74695064528407</t>
+          <t>62.74695064528737</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -8256,12 +8331,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8276,7 +8351,7 @@
       </c>
       <c r="CP16" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
+          <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
       <c r="CQ16" t="inlineStr">
@@ -8316,7 +8391,12 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="CY16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8358,12 +8438,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -8378,132 +8458,132 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-02-03 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>2026/01/09</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>28.05</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>27.9</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
           <t>2026-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2024-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2024-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>-9.45</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>2026/01/09</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -8534,7 +8614,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -8592,12 +8672,12 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-118.05</t>
+          <t>-125.53</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8607,7 +8687,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>759.7741935483871</t>
+          <t>623.0523012552302</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -8633,12 +8713,12 @@
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>14.76190532123708</t>
+          <t>14.76190532125441</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-31.06679989192241</t>
+          <t>-31.06679989191866</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -8748,12 +8828,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8768,7 +8848,7 @@
       </c>
       <c r="CP17" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
+          <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
       <c r="CQ17" t="inlineStr">
@@ -8808,7 +8888,12 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="CY17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8850,12 +8935,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -8870,132 +8955,132 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-02-03 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>2026/01/09</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>28.05</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>27.9</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
           <t>2026-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2024-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2024-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>-9.45</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>2026/01/09</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -9026,7 +9111,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -9084,12 +9169,12 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-114.62</t>
+          <t>-120.68</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9099,7 +9184,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>759.7741935483871</t>
+          <t>623.0523012552302</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -9125,12 +9210,12 @@
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>23.09439717817517</t>
+          <t>23.09439717819497</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-11.72691494893456</t>
+          <t>-11.7269149489303</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -9240,12 +9325,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9260,7 +9345,7 @@
       </c>
       <c r="CP18" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
+          <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
       <c r="CQ18" t="inlineStr">
@@ -9300,7 +9385,12 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="CY18" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9342,12 +9432,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -9362,132 +9452,132 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-02-03 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>2026/01/09</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>28.05</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>27.9</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
           <t>2026-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2024-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2024-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>-9.45</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>2026/01/09</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -9518,7 +9608,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9576,12 +9666,12 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-111.01</t>
+          <t>-115.58</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9591,7 +9681,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>759.7741935483871</t>
+          <t>623.0523012552302</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -9617,12 +9707,12 @@
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>29.42554483764966</t>
+          <t>29.42554483767229</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>25.42745336065286</t>
+          <t>25.42745336065769</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -9732,12 +9822,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9752,7 +9842,7 @@
       </c>
       <c r="CP19" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
+          <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
       <c r="CQ19" t="inlineStr">
@@ -9792,7 +9882,12 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="CY19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9929,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -9854,132 +9949,132 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-02-03 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>2026/01/09</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>28.05</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>27.9</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
           <t>2026-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2024-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2024-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>-9.45</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>2026/01/09</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -10010,7 +10105,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -10068,12 +10163,12 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-106.29</t>
+          <t>-108.89</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -10083,7 +10178,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>759.7741935483871</t>
+          <t>623.0523012552302</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
@@ -10109,12 +10204,12 @@
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>30.15247056073999</t>
+          <t>30.15247056076586</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>53.1684276114687</t>
+          <t>53.16842761147421</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -10189,7 +10284,7 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -10224,12 +10319,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10244,7 +10339,7 @@
       </c>
       <c r="CP20" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
+          <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
       <c r="CQ20" t="inlineStr">
@@ -10284,7 +10379,12 @@
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CY20" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10326,12 +10426,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -10346,132 +10446,132 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-02-03 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>2026/01/09</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>28.05</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>27.9</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
           <t>2026-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2024-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2024-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>-9.45</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>2026/01/09</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -10502,7 +10602,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10549,7 +10649,7 @@
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-15530.29</t>
+          <t>-15530.13</t>
         </is>
       </c>
       <c r="BD21" t="n">
@@ -10560,12 +10660,12 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-100.21</t>
+          <t>-100.30</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10575,7 +10675,7 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>759.7741935483871</t>
+          <t>623.0523012552302</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
@@ -10601,12 +10701,12 @@
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>25.96775109697113</t>
+          <t>25.9677510970007</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>61.64951841222461</t>
+          <t>61.64951841223092</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -10681,7 +10781,7 @@
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -10716,12 +10816,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10736,7 +10836,7 @@
       </c>
       <c r="CP21" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
+          <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
       <c r="CQ21" t="inlineStr">
@@ -10776,7 +10876,12 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CY21" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10818,12 +10923,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -10838,132 +10943,132 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-02-03 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>28.45</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>2026/01/09</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>28.05</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>27.9</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
           <t>2026-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2024-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2024-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>-9.45</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>28.3</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>2026/01/09</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -10994,7 +11099,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -11052,12 +11157,12 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-92.11</t>
+          <t>-88.84</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -11067,7 +11172,7 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>759.7741935483871</t>
+          <t>623.0523012552302</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -11093,12 +11198,12 @@
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>19.48015703965232</t>
+          <t>19.48015703968611</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>10.38502247001077</t>
+          <t>10.38502247001799</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -11208,12 +11313,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11228,7 +11333,7 @@
       </c>
       <c r="CP22" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
+          <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
       <c r="CQ22" t="inlineStr">
@@ -11268,7 +11373,12 @@
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CY22" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -11280,17 +11390,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>82828.243</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11300,7 +11410,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11310,17 +11420,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>36.41</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11330,37 +11440,37 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-02-03 00:00:00</t>
+          <t>2025-12-24 00:00:00</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-02-04 00:00:00</t>
+          <t>2026-01-22 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2024-11-19 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2024-12-02 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -11370,12 +11480,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -11385,22 +11495,22 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025/11/07</t>
+          <t>2025/08/07</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -11410,37 +11520,37 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2025/11/11</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025/11/03</t>
+          <t>2025/06/24</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2026/01/09</t>
+          <t>2026/01/22</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
@@ -11450,27 +11560,27 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-08-01 00:00:00</t>
+          <t>2025-12-26 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>22.72</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11481,121 +11591,121 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>573</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>82828</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-0.78</v>
+        <v>-6.3</v>
       </c>
       <c r="AV23" t="n">
-        <v>-1.58</v>
+        <v>-1.01</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>16.22</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>28.22</t>
+          <t>40.18</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>28.67</v>
+        <v>40.59</v>
       </c>
       <c r="BA23" t="n">
-        <v>28.38</v>
+        <v>34.92</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>33.08</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-196.08</t>
+          <t>-38.14</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.06</v>
+        <v>1.23</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.06</v>
+        <v>1.99</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-81.47</t>
+          <t>-25.31</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026/01/29</t>
+          <t>2025/12/24</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>759.7741935483871</t>
+          <t>2975586904.290837</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>921.0</t>
+          <t>3117063989.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>550.2</v>
+        <v>9298675857.799999</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>403.35</t>
+          <t>7355091659.9</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>328.01</v>
+        <v>4891441156.32</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>1943584197</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>21.13381787049624</t>
+          <t>418216189.9795332</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>50.67199175006198</t>
+          <t>33942859.99032688</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>921.0</t>
+          <t>3117063989.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11605,57 +11715,57 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2026/01/02</t>
+          <t>2025/12/22</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-8.20</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>唐榮公司</t>
+          <t>華新</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
         <is>
-          <t>唐榮公司</t>
+          <t>華新</t>
         </is>
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>鋼鐵工業</t>
+          <t>電器電纜</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
         <is>
-          <t>29.8389724126963</t>
+          <t>21.59621922590888</t>
         </is>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>0.4355880318993286</t>
+          <t>13.61749793509646</t>
         </is>
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>-21.22308305261796</t>
+          <t>-2.747769410820856</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
@@ -11665,92 +11775,92 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>104.58</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>-11.19%</t>
+          <t>4.76%</t>
         </is>
       </c>
       <c r="CK23" t="inlineStr">
         <is>
-          <t>-14.27%</t>
+          <t>-1.56%</t>
         </is>
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>166840</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
         <is>
-          <t>不�袗�100.00% (2024年)</t>
+          <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
       <c r="CO23" t="inlineStr">
         <is>
-          <t>唐榮公司-鋼鐵工業-上櫃</t>
+          <t>華新-電器電纜-上市</t>
         </is>
       </c>
       <c r="CP23" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
+          <t>電器電纜右上上市</t>
         </is>
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="CV23" t="inlineStr">
         <is>
-          <t>** 鋼鐵 - 不鏽鋼胚</t>
+          <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
       <c r="CW23" t="inlineStr">
@@ -11760,7 +11870,12 @@
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY23" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -11802,12 +11917,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -11822,7 +11937,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11973,12 +12088,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>1,299</t>
+          <t>573</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>209507</t>
+          <t>82828</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -12051,7 +12166,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>1897316507.997041</t>
+          <t>2975586904.290837</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -12077,12 +12192,12 @@
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>488084068.1593871</t>
+          <t>488084068.1593889</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>528522192.4529905</t>
+          <t>528522192.4529915</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
@@ -12132,7 +12247,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12167,7 +12282,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12177,7 +12292,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>101.67</t>
+          <t>104.58</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12192,12 +12307,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>162187</t>
+          <t>166840</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12252,7 +12367,12 @@
       </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY24" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -12294,12 +12414,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -12314,7 +12434,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12465,12 +12585,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>1,299</t>
+          <t>573</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>209507</t>
+          <t>82828</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12543,7 +12663,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>1897316507.997041</t>
+          <t>2975586904.290837</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -12569,12 +12689,12 @@
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>480731681.9241865</t>
+          <t>480731681.9241884</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>701126070.9191914</t>
+          <t>701126070.9191923</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
@@ -12624,7 +12744,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12659,7 +12779,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12669,7 +12789,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>101.67</t>
+          <t>104.58</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12684,12 +12804,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>162187</t>
+          <t>166840</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12744,7 +12864,12 @@
       </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY25" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -12786,12 +12911,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-18.85</t>
+          <t>-15.54</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -12806,7 +12931,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12957,12 +13082,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>1,299</t>
+          <t>573</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>209507</t>
+          <t>82828</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12997,7 +13122,7 @@
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>40.39</v>
+        <v>40.38</v>
       </c>
       <c r="BA26" t="n">
         <v>34.39</v>
@@ -13035,7 +13160,7 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>1897316507.997041</t>
+          <t>2975586904.290837</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
@@ -13061,12 +13186,12 @@
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>440659974.8341856</t>
+          <t>440659974.8341877</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>986430786.9095078</t>
+          <t>986430786.9095087</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
@@ -13116,7 +13241,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13151,7 +13276,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13161,7 +13286,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>101.67</t>
+          <t>104.58</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13176,12 +13301,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>162187</t>
+          <t>166840</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13236,7 +13361,12 @@
       </c>
       <c r="CX26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY26" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -13278,12 +13408,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-20.22</t>
+          <t>-16.87</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -13298,7 +13428,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13449,12 +13579,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>1,299</t>
+          <t>573</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>209507</t>
+          <t>82828</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13527,7 +13657,7 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>1897316507.997041</t>
+          <t>2975586904.290837</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
@@ -13553,12 +13683,12 @@
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>341428918.093218</t>
+          <t>341428918.0932202</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>460169621.4703341</t>
+          <t>460169621.470335</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
@@ -13608,7 +13738,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13643,7 +13773,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13653,7 +13783,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>101.67</t>
+          <t>104.58</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13668,12 +13798,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>162187</t>
+          <t>166840</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13728,7 +13858,12 @@
       </c>
       <c r="CX27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY27" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -13770,12 +13905,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-17.49</t>
+          <t>-14.21</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -13790,7 +13925,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13941,12 +14076,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>1,299</t>
+          <t>573</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>209507</t>
+          <t>82828</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -14019,7 +14154,7 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>1897316507.997041</t>
+          <t>2975586904.290837</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
@@ -14045,12 +14180,12 @@
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>319839699.2973787</t>
+          <t>319839699.2973811</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>46519899.86185932</t>
+          <t>46519899.86186028</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
@@ -14100,7 +14235,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -14135,7 +14270,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14145,7 +14280,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>101.67</t>
+          <t>104.58</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14160,12 +14295,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>162187</t>
+          <t>166840</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14220,7 +14355,12 @@
       </c>
       <c r="CX28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY28" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -14262,12 +14402,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-10.93</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -14282,7 +14422,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -14433,12 +14573,12 @@
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>1,299</t>
+          <t>573</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>209507</t>
+          <t>82828</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -14511,7 +14651,7 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>1897316507.997041</t>
+          <t>2975586904.290837</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
@@ -14537,12 +14677,12 @@
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>369534208.285655</t>
+          <t>369534208.2856576</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>-414007688.8595991</t>
+          <t>-414007688.8595982</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
@@ -14592,7 +14732,7 @@
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -14627,7 +14767,7 @@
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -14637,7 +14777,7 @@
       </c>
       <c r="CI29" t="inlineStr">
         <is>
-          <t>101.67</t>
+          <t>104.58</t>
         </is>
       </c>
       <c r="CJ29" t="inlineStr">
@@ -14652,12 +14792,12 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
         <is>
-          <t>162187</t>
+          <t>166840</t>
         </is>
       </c>
       <c r="CN29" t="inlineStr">
@@ -14712,7 +14852,12 @@
       </c>
       <c r="CX29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY29" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -14754,12 +14899,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -14774,7 +14919,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -14925,12 +15070,12 @@
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>1,299</t>
+          <t>573</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>209507</t>
+          <t>82828</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -15003,7 +15148,7 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>1897316507.997041</t>
+          <t>2975586904.290837</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
@@ -15029,12 +15174,12 @@
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>511996371.402974</t>
+          <t>511996371.4029769</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>-349370636.7166977</t>
+          <t>-349370636.7166967</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
@@ -15084,7 +15229,7 @@
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -15119,7 +15264,7 @@
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -15129,7 +15274,7 @@
       </c>
       <c r="CI30" t="inlineStr">
         <is>
-          <t>101.67</t>
+          <t>104.58</t>
         </is>
       </c>
       <c r="CJ30" t="inlineStr">
@@ -15144,12 +15289,12 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
         <is>
-          <t>162187</t>
+          <t>166840</t>
         </is>
       </c>
       <c r="CN30" t="inlineStr">
@@ -15204,7 +15349,12 @@
       </c>
       <c r="CX30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY30" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -15246,12 +15396,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-6.15</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -15266,7 +15416,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -15417,12 +15567,12 @@
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>1,299</t>
+          <t>573</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>209507</t>
+          <t>82828</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -15495,7 +15645,7 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>1897316507.997041</t>
+          <t>2975586904.290837</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
@@ -15521,12 +15671,12 @@
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>668608554.6974597</t>
+          <t>668608554.697463</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>-169733736.7012424</t>
+          <t>-169733736.7012415</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
@@ -15576,7 +15726,7 @@
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -15601,7 +15751,7 @@
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
@@ -15611,7 +15761,7 @@
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -15621,7 +15771,7 @@
       </c>
       <c r="CI31" t="inlineStr">
         <is>
-          <t>101.67</t>
+          <t>104.58</t>
         </is>
       </c>
       <c r="CJ31" t="inlineStr">
@@ -15636,12 +15786,12 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
         <is>
-          <t>162187</t>
+          <t>166840</t>
         </is>
       </c>
       <c r="CN31" t="inlineStr">
@@ -15696,7 +15846,12 @@
       </c>
       <c r="CX31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY31" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -15738,12 +15893,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-6.69</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -15758,7 +15913,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -15909,12 +16064,12 @@
       <c r="AP32" t="inlineStr"/>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>1,299</t>
+          <t>573</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>209507</t>
+          <t>82828</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -15987,7 +16142,7 @@
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>1897316507.997041</t>
+          <t>2975586904.290837</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr">
@@ -16013,12 +16168,12 @@
       </c>
       <c r="BO32" t="inlineStr">
         <is>
-          <t>821034425.8608601</t>
+          <t>821034425.8608639</t>
         </is>
       </c>
       <c r="BP32" t="inlineStr">
         <is>
-          <t>228416658.9173107</t>
+          <t>228416658.9173117</t>
         </is>
       </c>
       <c r="BQ32" t="inlineStr">
@@ -16068,7 +16223,7 @@
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -16093,7 +16248,7 @@
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
@@ -16103,7 +16258,7 @@
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -16113,7 +16268,7 @@
       </c>
       <c r="CI32" t="inlineStr">
         <is>
-          <t>101.67</t>
+          <t>104.58</t>
         </is>
       </c>
       <c r="CJ32" t="inlineStr">
@@ -16128,12 +16283,12 @@
       </c>
       <c r="CL32" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="CM32" t="inlineStr">
         <is>
-          <t>162187</t>
+          <t>166840</t>
         </is>
       </c>
       <c r="CN32" t="inlineStr">
@@ -16188,7 +16343,12 @@
       </c>
       <c r="CX32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY32" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -16230,12 +16390,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-8.33</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -16250,7 +16410,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -16401,12 +16561,12 @@
       <c r="AP33" t="inlineStr"/>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>1,299</t>
+          <t>573</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>209507</t>
+          <t>82828</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -16479,7 +16639,7 @@
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>1897316507.997041</t>
+          <t>2975586904.290837</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr">
@@ -16505,12 +16665,12 @@
       </c>
       <c r="BO33" t="inlineStr">
         <is>
-          <t>928783110.7596873</t>
+          <t>928783110.7596917</t>
         </is>
       </c>
       <c r="BP33" t="inlineStr">
         <is>
-          <t>549774450.9467697</t>
+          <t>549774450.9467707</t>
         </is>
       </c>
       <c r="BQ33" t="inlineStr">
@@ -16560,7 +16720,7 @@
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -16595,7 +16755,7 @@
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -16605,7 +16765,7 @@
       </c>
       <c r="CI33" t="inlineStr">
         <is>
-          <t>101.67</t>
+          <t>104.58</t>
         </is>
       </c>
       <c r="CJ33" t="inlineStr">
@@ -16620,12 +16780,12 @@
       </c>
       <c r="CL33" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="CM33" t="inlineStr">
         <is>
-          <t>162187</t>
+          <t>166840</t>
         </is>
       </c>
       <c r="CN33" t="inlineStr">
@@ -16680,499 +16840,12 @@
       </c>
       <c r="CX33" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>【b1】</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1605</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>137727.22</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>42.4</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-15.85</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>4.98</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2025-12-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2026-01-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>39.05</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>33.97</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>8.58</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>2026/01/22</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>39.05</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>2025-12-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>37.79</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>1,299</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>209507</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>71.64</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr">
-        <is>
-          <t>73.9</t>
-        </is>
-      </c>
-      <c r="AU34" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>15.91</v>
-      </c>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>11.85</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>5.15</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
-      </c>
-      <c r="AZ34" t="n">
-        <v>36.68</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="BB34" t="inlineStr">
-        <is>
-          <t>31.19</t>
-        </is>
-      </c>
-      <c r="BC34" t="inlineStr">
-        <is>
-          <t>22.24</t>
-        </is>
-      </c>
-      <c r="BD34" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
-        <is>
-          <t>-2.42</t>
-        </is>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2025/12/24</t>
-        </is>
-      </c>
-      <c r="BI34" t="inlineStr">
-        <is>
-          <t>1897316507.997041</t>
-        </is>
-      </c>
-      <c r="BJ34" t="inlineStr">
-        <is>
-          <t>5800847007.0</t>
-        </is>
-      </c>
-      <c r="BK34" t="n">
-        <v>9772822696.6</v>
-      </c>
-      <c r="BL34" t="inlineStr">
-        <is>
-          <t>9309465606.0</t>
-        </is>
-      </c>
-      <c r="BM34" t="n">
-        <v>4248695916.46</v>
-      </c>
-      <c r="BN34" t="inlineStr">
-        <is>
-          <t>463357090</t>
-        </is>
-      </c>
-      <c r="BO34" t="inlineStr">
-        <is>
-          <t>997693776.1802177</t>
-        </is>
-      </c>
-      <c r="BP34" t="inlineStr">
-        <is>
-          <t>813437134.9193249</t>
-        </is>
-      </c>
-      <c r="BQ34" t="inlineStr">
-        <is>
-          <t>5800847007.0</t>
-        </is>
-      </c>
-      <c r="BR34" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="BS34" t="inlineStr">
-        <is>
-          <t>30.45</t>
-        </is>
-      </c>
-      <c r="BT34" t="inlineStr">
-        <is>
-          <t>2025/12/22</t>
-        </is>
-      </c>
-      <c r="BU34" t="inlineStr">
-        <is>
-          <t>39.24</t>
-        </is>
-      </c>
-      <c r="BV34" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BW34" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BX34" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BY34" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ34" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="CA34" t="inlineStr">
-        <is>
-          <t>21.59621922590888</t>
-        </is>
-      </c>
-      <c r="CB34" t="inlineStr">
-        <is>
-          <t>13.61749793509646</t>
-        </is>
-      </c>
-      <c r="CC34" t="inlineStr">
-        <is>
-          <t>-2.747769410820856</t>
-        </is>
-      </c>
-      <c r="CD34" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE34" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF34" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="CG34" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="CH34" t="inlineStr">
-        <is>
-          <t>9.28</t>
-        </is>
-      </c>
-      <c r="CI34" t="inlineStr">
-        <is>
-          <t>101.67</t>
-        </is>
-      </c>
-      <c r="CJ34" t="inlineStr">
-        <is>
-          <t>4.76%</t>
-        </is>
-      </c>
-      <c r="CK34" t="inlineStr">
-        <is>
-          <t>-1.56%</t>
-        </is>
-      </c>
-      <c r="CL34" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
-      <c r="CM34" t="inlineStr">
-        <is>
-          <t>162187</t>
-        </is>
-      </c>
-      <c r="CN34" t="inlineStr">
-        <is>
-          <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO34" t="inlineStr">
-        <is>
-          <t>華新-電器電纜-上市</t>
-        </is>
-      </c>
-      <c r="CP34" t="inlineStr">
-        <is>
-          <t>電器電纜右上上市</t>
-        </is>
-      </c>
-      <c r="CQ34" t="inlineStr">
-        <is>
-          <t>41.55</t>
-        </is>
-      </c>
-      <c r="CR34" t="inlineStr">
-        <is>
-          <t>43.05</t>
-        </is>
-      </c>
-      <c r="CS34" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="CT34" t="inlineStr">
-        <is>
-          <t>42.4</t>
-        </is>
-      </c>
-      <c r="CU34" t="inlineStr">
-        <is>
-          <t>35.05</t>
-        </is>
-      </c>
-      <c r="CV34" t="inlineStr">
-        <is>
-          <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
-        </is>
-      </c>
-      <c r="CW34" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="CX34" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY33" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
